--- a/danish_grid_graph_ready.xlsx
+++ b/danish_grid_graph_ready.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Master\Semester3\Advanced Business Analytics\Critical-Energy-Infrastructure-Under-Hybrid-War-Scenarios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9410CE80-0F62-4E32-A862-8E32869C3263}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76670474-4D66-4255-99E2-489F9125F85E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38460" yWindow="-21720" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38460" yWindow="-21720" windowWidth="38640" windowHeight="21240" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="nodes" sheetId="1" r:id="rId1"/>
     <sheet name="edges" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">edges!$A$1:$AE$439</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">nodes!$A$1:$N$301</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5104" uniqueCount="1836">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4308" uniqueCount="1657">
   <si>
     <t>bus_index</t>
   </si>
@@ -4815,724 +4816,187 @@
     <t>5,06</t>
   </si>
   <si>
-    <t>transformer2</t>
-  </si>
-  <si>
     <t>transformer</t>
   </si>
   <si>
     <t>AMV_132_010_MT1</t>
   </si>
   <si>
-    <t>144,0</t>
-  </si>
-  <si>
-    <t>11,0</t>
-  </si>
-  <si>
-    <t>100,0</t>
-  </si>
-  <si>
-    <t>7,07</t>
-  </si>
-  <si>
-    <t>170,0</t>
-  </si>
-  <si>
-    <t>54,8</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
     <t>AMV_132_0173_MT3</t>
   </si>
   <si>
-    <t>17,0</t>
-  </si>
-  <si>
-    <t>300,0</t>
-  </si>
-  <si>
-    <t>450,0</t>
-  </si>
-  <si>
-    <t>143,0</t>
-  </si>
-  <si>
     <t>ASV_132_0122_MT2</t>
   </si>
   <si>
-    <t>144,1</t>
-  </si>
-  <si>
-    <t>12,0</t>
-  </si>
-  <si>
-    <t>159,0</t>
-  </si>
-  <si>
-    <t>222,6</t>
-  </si>
-  <si>
-    <t>0,60</t>
-  </si>
-  <si>
-    <t>88,0</t>
-  </si>
-  <si>
     <t>ASV_4001_132_T41B</t>
   </si>
   <si>
-    <t>400,0</t>
-  </si>
-  <si>
-    <t>132,0</t>
-  </si>
-  <si>
-    <t>500,0</t>
-  </si>
-  <si>
-    <t>14,50</t>
-  </si>
-  <si>
-    <t>950,0</t>
-  </si>
-  <si>
-    <t>187,9</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>V</t>
-  </si>
-  <si>
     <t>ASV_400_0215_MT5</t>
   </si>
   <si>
-    <t>425,0</t>
-  </si>
-  <si>
-    <t>21,0</t>
-  </si>
-  <si>
-    <t>750,0</t>
-  </si>
-  <si>
-    <t>13,90</t>
-  </si>
-  <si>
-    <t>1125,0</t>
-  </si>
-  <si>
-    <t>235,0</t>
-  </si>
-  <si>
     <t>ASV_400_4001_T41A</t>
   </si>
   <si>
-    <t>50,0</t>
-  </si>
-  <si>
-    <t>0,0</t>
-  </si>
-  <si>
     <t>AVV_1321_132_T41B</t>
   </si>
   <si>
-    <t>53,1</t>
-  </si>
-  <si>
-    <t>37,2</t>
-  </si>
-  <si>
-    <t>27,1</t>
-  </si>
-  <si>
     <t>AVV_132_0171_MT1</t>
   </si>
   <si>
     <t>AVV_400_0201_MT2</t>
   </si>
   <si>
-    <t>19,5</t>
-  </si>
-  <si>
-    <t>558,0</t>
-  </si>
-  <si>
-    <t>12,80</t>
-  </si>
-  <si>
-    <t>669,6</t>
-  </si>
-  <si>
-    <t>250,0</t>
-  </si>
-  <si>
     <t>AVV_400_1321_T41A</t>
   </si>
   <si>
-    <t>11,33</t>
-  </si>
-  <si>
-    <t>68,7</t>
-  </si>
-  <si>
     <t>BJS_220_2201-T31</t>
   </si>
   <si>
-    <t>232,0</t>
-  </si>
-  <si>
     <t>BJS_400_016_T45</t>
   </si>
   <si>
-    <t>420,0</t>
-  </si>
-  <si>
-    <t>15,8</t>
-  </si>
-  <si>
-    <t>660,0</t>
-  </si>
-  <si>
-    <t>82,0</t>
-  </si>
-  <si>
-    <t>0,95</t>
-  </si>
-  <si>
     <t>BJS_400_132-T42</t>
   </si>
   <si>
-    <t>11,83</t>
-  </si>
-  <si>
-    <t>600,0</t>
-  </si>
-  <si>
-    <t>100,5</t>
-  </si>
-  <si>
     <t>BJS_400_132_T41</t>
   </si>
   <si>
-    <t>440,0</t>
-  </si>
-  <si>
-    <t>145,0</t>
-  </si>
-  <si>
-    <t>350,0</t>
-  </si>
-  <si>
-    <t>21,86</t>
-  </si>
-  <si>
-    <t>1225,0</t>
-  </si>
-  <si>
-    <t>217,5</t>
-  </si>
-  <si>
     <t>BJS_400_220-T43</t>
   </si>
   <si>
-    <t>410,0</t>
-  </si>
-  <si>
-    <t>13,70</t>
-  </si>
-  <si>
-    <t>47,5</t>
-  </si>
-  <si>
     <t>GØR_1321_132_T41B</t>
   </si>
   <si>
-    <t>85,1</t>
-  </si>
-  <si>
-    <t>76,6</t>
-  </si>
-  <si>
-    <t>41,8</t>
-  </si>
-  <si>
     <t>GØR_400_1321_T41A</t>
   </si>
   <si>
     <t>HCV_400_132_T41</t>
   </si>
   <si>
-    <t>13,56</t>
-  </si>
-  <si>
-    <t>665,0</t>
-  </si>
-  <si>
-    <t>73,3</t>
-  </si>
-  <si>
     <t>HVE_400_132_T41</t>
   </si>
   <si>
-    <t>21,81</t>
-  </si>
-  <si>
-    <t>1260,0</t>
-  </si>
-  <si>
-    <t>0,21</t>
-  </si>
-  <si>
-    <t>217,8</t>
-  </si>
-  <si>
     <t>HVE_400_132_T44</t>
   </si>
   <si>
-    <t>25,83</t>
-  </si>
-  <si>
-    <t>1750,0</t>
-  </si>
-  <si>
-    <t>191,0</t>
-  </si>
-  <si>
     <t>ISH_400_132_T41</t>
   </si>
   <si>
-    <t>26,75</t>
-  </si>
-  <si>
-    <t>1550,0</t>
-  </si>
-  <si>
-    <t>155,7</t>
-  </si>
-  <si>
-    <t>1,07</t>
-  </si>
-  <si>
     <t>ISH_400_220-T42</t>
   </si>
   <si>
     <t>KFE_010_000-T12</t>
   </si>
   <si>
-    <t>10,0</t>
-  </si>
-  <si>
-    <t>0,4</t>
-  </si>
-  <si>
-    <t>1,0</t>
-  </si>
-  <si>
-    <t>5,25</t>
-  </si>
-  <si>
-    <t>0,7</t>
-  </si>
-  <si>
     <t>KYV_132_0181_MT21</t>
   </si>
   <si>
-    <t>141,3</t>
-  </si>
-  <si>
-    <t>18,0</t>
-  </si>
-  <si>
-    <t>307,0</t>
-  </si>
-  <si>
-    <t>12,69</t>
-  </si>
-  <si>
-    <t>644,7</t>
-  </si>
-  <si>
-    <t>60,0</t>
-  </si>
-  <si>
     <t>KYV_132_0182_MT22</t>
   </si>
   <si>
-    <t>330,0</t>
-  </si>
-  <si>
     <t>LIN_132_132_T13</t>
   </si>
   <si>
-    <t>125,0</t>
-  </si>
-  <si>
-    <t>3,91</t>
-  </si>
-  <si>
-    <t>27,9</t>
-  </si>
-  <si>
     <t>RAD_132_009_T1</t>
   </si>
   <si>
-    <t>9,0</t>
-  </si>
-  <si>
-    <t>80,2</t>
-  </si>
-  <si>
-    <t>9,35</t>
-  </si>
-  <si>
-    <t>745,9</t>
-  </si>
-  <si>
-    <t>20,0</t>
-  </si>
-  <si>
     <t>STV_132_0182_MT2</t>
   </si>
   <si>
-    <t>144,3</t>
-  </si>
-  <si>
-    <t>310,0</t>
-  </si>
-  <si>
-    <t>12,60</t>
-  </si>
-  <si>
-    <t>713,0</t>
-  </si>
-  <si>
-    <t>172,0</t>
-  </si>
-  <si>
     <t>ØSV_400_132-KT41</t>
   </si>
   <si>
     <t>ABS_1501_150_KT31</t>
   </si>
   <si>
-    <t>165,0</t>
-  </si>
-  <si>
-    <t>59,1</t>
-  </si>
-  <si>
-    <t>29,8</t>
-  </si>
-  <si>
     <t>ASR_400_150_KT51</t>
   </si>
   <si>
-    <t>167,7</t>
-  </si>
-  <si>
-    <t>200,0</t>
-  </si>
-  <si>
-    <t>13,17</t>
-  </si>
-  <si>
-    <t>40,2</t>
-  </si>
-  <si>
     <t>EDR_400_150C_KT52</t>
   </si>
   <si>
-    <t>167,6</t>
-  </si>
-  <si>
-    <t>12,65</t>
-  </si>
-  <si>
-    <t>1120,0</t>
-  </si>
-  <si>
-    <t>79,0</t>
-  </si>
-  <si>
     <t>EDR_400_220-KT54</t>
   </si>
   <si>
-    <t>238,3</t>
-  </si>
-  <si>
-    <t>625,3</t>
-  </si>
-  <si>
-    <t>45,7</t>
-  </si>
-  <si>
     <t>FER_400_150_KT51</t>
   </si>
   <si>
-    <t>12,63</t>
-  </si>
-  <si>
-    <t>1000,0</t>
-  </si>
-  <si>
-    <t>73,5</t>
-  </si>
-  <si>
     <t>FGD_400_150_KT51</t>
   </si>
   <si>
-    <t>12,59</t>
-  </si>
-  <si>
-    <t>71,5</t>
-  </si>
-  <si>
     <t>FGD_400_150_KT52</t>
   </si>
   <si>
     <t>FVO_150_010_MT1</t>
   </si>
   <si>
-    <t>10,5</t>
-  </si>
-  <si>
-    <t>45,0</t>
-  </si>
-  <si>
-    <t>117,0</t>
-  </si>
-  <si>
-    <t>24,0</t>
-  </si>
-  <si>
     <t>FVO_400_021A_MT51</t>
   </si>
   <si>
-    <t>433,0</t>
-  </si>
-  <si>
-    <t>455,0</t>
-  </si>
-  <si>
-    <t>15,21</t>
-  </si>
-  <si>
-    <t>728,0</t>
-  </si>
-  <si>
     <t>HER_060_012_MT21</t>
   </si>
   <si>
-    <t>11,5</t>
-  </si>
-  <si>
-    <t>102,0</t>
-  </si>
-  <si>
-    <t>12,07</t>
-  </si>
-  <si>
-    <t>315,6</t>
-  </si>
-  <si>
-    <t>0,73</t>
-  </si>
-  <si>
-    <t>48,7</t>
-  </si>
-  <si>
     <t>IDU_400_150_KT51</t>
   </si>
   <si>
-    <t>12,68</t>
-  </si>
-  <si>
-    <t>960,0</t>
-  </si>
-  <si>
     <t>KAS_400_150_KT51</t>
   </si>
   <si>
-    <t>13,02</t>
-  </si>
-  <si>
-    <t>108,4</t>
-  </si>
-  <si>
     <t>KAS_400_150_KT52</t>
   </si>
   <si>
     <t>KIN_400_150_KT51</t>
   </si>
   <si>
-    <t>39,8</t>
-  </si>
-  <si>
     <t>LAG_400_150_KT51</t>
   </si>
   <si>
-    <t>73,8</t>
-  </si>
-  <si>
     <t>MAL_400_150_KT51</t>
   </si>
   <si>
-    <t>12,66</t>
-  </si>
-  <si>
     <t>MKS_150_019A_MT31</t>
   </si>
   <si>
-    <t>173,0</t>
-  </si>
-  <si>
-    <t>19,0</t>
-  </si>
-  <si>
-    <t>819,0</t>
-  </si>
-  <si>
     <t>MKS_400_019B_MT51</t>
   </si>
   <si>
-    <t>428,0</t>
-  </si>
-  <si>
-    <t>14,20</t>
-  </si>
-  <si>
     <t>NVV_150_021B_MT31</t>
   </si>
   <si>
-    <t>735,0</t>
-  </si>
-  <si>
     <t>NVV_400_021A_MT51</t>
   </si>
   <si>
-    <t>421,3</t>
-  </si>
-  <si>
-    <t>485,0</t>
-  </si>
-  <si>
-    <t>824,5</t>
-  </si>
-  <si>
     <t>NVV_400_150_KT51</t>
   </si>
   <si>
-    <t>12,58</t>
-  </si>
-  <si>
-    <t>69,7</t>
-  </si>
-  <si>
     <t>SHE_150_021_MT31</t>
   </si>
   <si>
-    <t>174,0</t>
-  </si>
-  <si>
-    <t>890,0</t>
-  </si>
-  <si>
-    <t>18,85</t>
-  </si>
-  <si>
-    <t>1691,0</t>
-  </si>
-  <si>
     <t>SVS_400_021_MT51</t>
   </si>
   <si>
-    <t>429,4</t>
-  </si>
-  <si>
-    <t>13,00</t>
-  </si>
-  <si>
     <t>TJE_010_010_HT3</t>
   </si>
   <si>
-    <t>6,0</t>
-  </si>
-  <si>
     <t>TJE_150_013_MT31</t>
   </si>
   <si>
-    <t>167,0</t>
-  </si>
-  <si>
-    <t>12,5</t>
-  </si>
-  <si>
-    <t>180,0</t>
-  </si>
-  <si>
-    <t>6,36</t>
-  </si>
-  <si>
-    <t>540,0</t>
-  </si>
-  <si>
     <t>TJE_400_150_KT51</t>
   </si>
   <si>
     <t>TRI_400_150_KT51</t>
   </si>
   <si>
-    <t>12,61</t>
-  </si>
-  <si>
-    <t>90,0</t>
-  </si>
-  <si>
     <t>TRI_400_220_KT53</t>
   </si>
   <si>
-    <t>13,66</t>
-  </si>
-  <si>
     <t>TRI_400_220_KT54</t>
   </si>
   <si>
-    <t>654,9</t>
-  </si>
-  <si>
-    <t>44,3</t>
-  </si>
-  <si>
     <t>VHA_400_150_KT51</t>
   </si>
   <si>
-    <t>595,1</t>
-  </si>
-  <si>
-    <t>64,2</t>
-  </si>
-  <si>
     <t>VKE_150_019_MT31</t>
-  </si>
-  <si>
-    <t>175,7</t>
-  </si>
-  <si>
-    <t>457,5</t>
-  </si>
-  <si>
-    <t>11,78</t>
-  </si>
-  <si>
-    <t>640,5</t>
-  </si>
-  <si>
-    <t>transformer3</t>
   </si>
   <si>
     <t>Germany</t>
@@ -5907,14 +5371,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q301"/>
+  <dimension ref="A1:N301"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="33.6640625" customWidth="1"/>
     <col min="8" max="8" width="18.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5958,7 +5422,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>0</v>
       </c>
@@ -5981,7 +5445,7 @@
         <v>218</v>
       </c>
       <c r="H2" t="s">
-        <v>1833</v>
+        <v>1654</v>
       </c>
       <c r="I2" t="s">
         <v>343</v>
@@ -5998,11 +5462,8 @@
       <c r="N2">
         <v>12.8780796702535</v>
       </c>
-      <c r="Q2">
-        <v>6139.2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -6025,7 +5486,7 @@
         <v>218</v>
       </c>
       <c r="H3" t="s">
-        <v>1833</v>
+        <v>1654</v>
       </c>
       <c r="I3" t="s">
         <v>345</v>
@@ -6042,11 +5503,8 @@
       <c r="N3">
         <v>12.8780796702535</v>
       </c>
-      <c r="Q3">
-        <v>-147.62</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2</v>
       </c>
@@ -6069,7 +5527,7 @@
         <v>218</v>
       </c>
       <c r="H4" t="s">
-        <v>1833</v>
+        <v>1654</v>
       </c>
       <c r="I4" t="s">
         <v>448</v>
@@ -6086,12 +5544,8 @@
       <c r="N4">
         <v>12.7085299819776</v>
       </c>
-      <c r="Q4">
-        <f>Q2+Q3</f>
-        <v>5991.58</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>3</v>
       </c>
@@ -6114,7 +5568,7 @@
         <v>218</v>
       </c>
       <c r="H5" t="s">
-        <v>1833</v>
+        <v>1654</v>
       </c>
       <c r="I5" t="s">
         <v>449</v>
@@ -6132,7 +5586,7 @@
         <v>12.7085299819776</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>4</v>
       </c>
@@ -6155,7 +5609,7 @@
         <v>15</v>
       </c>
       <c r="H6" t="s">
-        <v>1832</v>
+        <v>1653</v>
       </c>
       <c r="I6" t="s">
         <v>68</v>
@@ -6173,7 +5627,7 @@
         <v>9.4109070012502993</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>5</v>
       </c>
@@ -6196,7 +5650,7 @@
         <v>15</v>
       </c>
       <c r="H7" t="s">
-        <v>1832</v>
+        <v>1653</v>
       </c>
       <c r="I7" t="s">
         <v>105</v>
@@ -6214,7 +5668,7 @@
         <v>9.4109070012502993</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>6</v>
       </c>
@@ -6237,7 +5691,7 @@
         <v>15</v>
       </c>
       <c r="H8" t="s">
-        <v>1832</v>
+        <v>1653</v>
       </c>
       <c r="I8" t="s">
         <v>149</v>
@@ -6255,7 +5709,7 @@
         <v>9.4109070012502993</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>7</v>
       </c>
@@ -6278,7 +5732,7 @@
         <v>15</v>
       </c>
       <c r="H9" t="s">
-        <v>1832</v>
+        <v>1653</v>
       </c>
       <c r="I9" t="s">
         <v>245</v>
@@ -6296,7 +5750,7 @@
         <v>9.2004788539427604</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>8</v>
       </c>
@@ -6319,7 +5773,7 @@
         <v>15</v>
       </c>
       <c r="H10" t="s">
-        <v>1832</v>
+        <v>1653</v>
       </c>
       <c r="I10" t="s">
         <v>350</v>
@@ -6331,7 +5785,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>9</v>
       </c>
@@ -6342,7 +5796,7 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <v>235</v>
+        <v>229.34931261402116</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -6354,7 +5808,7 @@
         <v>218</v>
       </c>
       <c r="H11" t="s">
-        <v>1832</v>
+        <v>1653</v>
       </c>
       <c r="I11" t="s">
         <v>477</v>
@@ -6366,7 +5820,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -6377,7 +5831,7 @@
         <v>0</v>
       </c>
       <c r="D12">
-        <v>546</v>
+        <v>532.8711688819385</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -6389,7 +5843,7 @@
         <v>15</v>
       </c>
       <c r="H12" t="s">
-        <v>1834</v>
+        <v>1655</v>
       </c>
       <c r="I12" t="s">
         <v>536</v>
@@ -6404,7 +5858,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -6415,7 +5869,7 @@
         <v>0</v>
       </c>
       <c r="D13">
-        <v>350</v>
+        <v>341.58408261662726</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -6427,7 +5881,7 @@
         <v>15</v>
       </c>
       <c r="H13" t="s">
-        <v>1832</v>
+        <v>1653</v>
       </c>
       <c r="I13" t="s">
         <v>539</v>
@@ -6442,7 +5896,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -6465,7 +5919,7 @@
         <v>15</v>
       </c>
       <c r="H14" t="s">
-        <v>1833</v>
+        <v>1654</v>
       </c>
       <c r="I14" t="s">
         <v>542</v>
@@ -6486,7 +5940,7 @@
         <v>11.910574835247999</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -6509,7 +5963,7 @@
         <v>15</v>
       </c>
       <c r="H15" t="s">
-        <v>1833</v>
+        <v>1654</v>
       </c>
       <c r="I15" t="s">
         <v>545</v>
@@ -6530,7 +5984,7 @@
         <v>11.910574835247999</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -6635,7 +6089,7 @@
         <v>15</v>
       </c>
       <c r="H18" t="s">
-        <v>1835</v>
+        <v>1656</v>
       </c>
       <c r="I18" t="s">
         <v>552</v>
@@ -6673,7 +6127,7 @@
         <v>15</v>
       </c>
       <c r="H19" t="s">
-        <v>1835</v>
+        <v>1656</v>
       </c>
       <c r="I19" t="s">
         <v>555</v>
@@ -6711,7 +6165,7 @@
         <v>15</v>
       </c>
       <c r="H20" t="s">
-        <v>1835</v>
+        <v>1656</v>
       </c>
       <c r="I20" t="s">
         <v>557</v>
@@ -6749,7 +6203,7 @@
         <v>15</v>
       </c>
       <c r="H21" t="s">
-        <v>1835</v>
+        <v>1656</v>
       </c>
       <c r="I21" t="s">
         <v>558</v>
@@ -6775,7 +6229,7 @@
         <v>0</v>
       </c>
       <c r="D22">
-        <v>74.8</v>
+        <v>73.001398227782047</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -6787,7 +6241,7 @@
         <v>218</v>
       </c>
       <c r="H22" t="s">
-        <v>1832</v>
+        <v>1653</v>
       </c>
       <c r="I22" t="s">
         <v>479</v>
@@ -7555,7 +7009,7 @@
         <v>21.21</v>
       </c>
       <c r="D46">
-        <v>58</v>
+        <v>56.605362262183945</v>
       </c>
       <c r="E46">
         <v>0</v>
@@ -7640,7 +7094,7 @@
         <v>0.26</v>
       </c>
       <c r="D48">
-        <v>71.599999999999994</v>
+        <v>69.878343758144311</v>
       </c>
       <c r="E48">
         <v>0</v>
@@ -7766,7 +7220,7 @@
         <v>18.97</v>
       </c>
       <c r="D51">
-        <v>52.9</v>
+        <v>51.627994201198803</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -8305,7 +7759,7 @@
         <v>1.41</v>
       </c>
       <c r="D64">
-        <v>22.3</v>
+        <v>21.763785835287965</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -8349,7 +7803,7 @@
         <v>0.59</v>
       </c>
       <c r="D65">
-        <v>12.4</v>
+        <v>12.101836069846224</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -8393,7 +7847,7 @@
         <v>0</v>
       </c>
       <c r="D66">
-        <v>53.7</v>
+        <v>52.408757818608244</v>
       </c>
       <c r="E66">
         <v>0</v>
@@ -8642,7 +8096,7 @@
         <v>10.06</v>
       </c>
       <c r="D72">
-        <v>52</v>
+        <v>50.749635131613196</v>
       </c>
       <c r="E72">
         <v>0</v>
@@ -8686,7 +8140,7 @@
         <v>10.94</v>
       </c>
       <c r="D73">
-        <v>50.5</v>
+        <v>49.285703348970507</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -8730,7 +8184,7 @@
         <v>0.21</v>
       </c>
       <c r="D74">
-        <v>74.7</v>
+        <v>72.903802775605882</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -8856,7 +8310,7 @@
         <v>0</v>
       </c>
       <c r="D77">
-        <v>22.1</v>
+        <v>21.56859493093561</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -8900,7 +8354,7 @@
         <v>33.049999999999997</v>
       </c>
       <c r="D78">
-        <v>71.2</v>
+        <v>69.487961949439608</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -8944,7 +8398,7 @@
         <v>6.74</v>
       </c>
       <c r="D79">
-        <v>22.8</v>
+        <v>22.251763096168862</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -9029,7 +8483,7 @@
         <v>0</v>
       </c>
       <c r="D81">
-        <v>25.3</v>
+        <v>24.691649400573343</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -9073,7 +8527,7 @@
         <v>0</v>
       </c>
       <c r="D82">
-        <v>9.5</v>
+        <v>9.2715679567370266</v>
       </c>
       <c r="E82">
         <v>0</v>
@@ -9199,7 +8653,7 @@
         <v>13.24</v>
       </c>
       <c r="D85">
-        <v>129.4</v>
+        <v>126.28851511597591</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -9284,7 +8738,7 @@
         <v>0</v>
       </c>
       <c r="D87">
-        <v>22.3</v>
+        <v>21.763785835287965</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -9454,7 +8908,7 @@
         <v>3.72</v>
       </c>
       <c r="D91">
-        <v>30.5</v>
+        <v>29.766612913734662</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -9498,7 +8952,7 @@
         <v>10.67</v>
       </c>
       <c r="D92">
-        <v>101.1</v>
+        <v>98.66900215011718</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -9583,7 +9037,7 @@
         <v>16.53</v>
       </c>
       <c r="D94">
-        <v>27.5</v>
+        <v>26.838749348449287</v>
       </c>
       <c r="E94">
         <v>0</v>
@@ -9627,7 +9081,7 @@
         <v>4.62</v>
       </c>
       <c r="D95">
-        <v>60.6</v>
+        <v>59.142844018764606</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -9794,7 +9248,7 @@
         <v>0</v>
       </c>
       <c r="D99">
-        <v>4.9000000000000004</v>
+        <v>4.7821771566327822</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -9838,7 +9292,7 @@
         <v>0.45</v>
       </c>
       <c r="D100">
-        <v>18.899999999999999</v>
+        <v>18.44554046129787</v>
       </c>
       <c r="E100">
         <v>0</v>
@@ -9882,7 +9336,7 @@
         <v>0</v>
       </c>
       <c r="D101">
-        <v>13.9</v>
+        <v>13.565767852488912</v>
       </c>
       <c r="E101">
         <v>0</v>
@@ -10005,7 +9459,7 @@
         <v>0.11</v>
       </c>
       <c r="D104">
-        <v>19.600000000000001</v>
+        <v>19.128708626531129</v>
       </c>
       <c r="E104">
         <v>0</v>
@@ -10213,7 +9667,7 @@
         <v>9.25</v>
       </c>
       <c r="D109">
-        <v>40.9</v>
+        <v>39.916539940057298</v>
       </c>
       <c r="E109">
         <v>0</v>
@@ -10257,7 +9711,7 @@
         <v>0.06</v>
       </c>
       <c r="D110">
-        <v>13.3</v>
+        <v>12.980195139431837</v>
       </c>
       <c r="E110">
         <v>0</v>
@@ -10301,7 +9755,7 @@
         <v>5.67</v>
       </c>
       <c r="D111">
-        <v>25.5</v>
+        <v>24.886840304925702</v>
       </c>
       <c r="E111">
         <v>0</v>
@@ -10386,7 +9840,7 @@
         <v>0</v>
       </c>
       <c r="D113">
-        <v>26.6</v>
+        <v>25.960390278863674</v>
       </c>
       <c r="E113">
         <v>0</v>
@@ -10717,7 +10171,7 @@
         <v>0.17</v>
       </c>
       <c r="D121">
-        <v>6.4</v>
+        <v>6.2461089392754703</v>
       </c>
       <c r="E121">
         <v>0</v>
@@ -10761,7 +10215,7 @@
         <v>0.85</v>
       </c>
       <c r="D122">
-        <v>6.3</v>
+        <v>6.148513487099291</v>
       </c>
       <c r="E122">
         <v>0</v>
@@ -11054,7 +10508,7 @@
         <v>0</v>
       </c>
       <c r="D129">
-        <v>54</v>
+        <v>52.701544175136782</v>
       </c>
       <c r="E129">
         <v>0</v>
@@ -11095,7 +10549,7 @@
         <v>0.02</v>
       </c>
       <c r="D130">
-        <v>8.6</v>
+        <v>8.3932088871514132</v>
       </c>
       <c r="E130">
         <v>0</v>
@@ -11139,7 +10593,7 @@
         <v>0</v>
       </c>
       <c r="D131">
-        <v>0.8</v>
+        <v>0.78076361740943379</v>
       </c>
       <c r="E131">
         <v>0</v>
@@ -11183,7 +10637,7 @@
         <v>0</v>
       </c>
       <c r="D132">
-        <v>20.2</v>
+        <v>19.714281339588201</v>
       </c>
       <c r="E132">
         <v>0</v>
@@ -11224,7 +10678,7 @@
         <v>3.78</v>
       </c>
       <c r="D133">
-        <v>23.6</v>
+        <v>23.032526713578296</v>
       </c>
       <c r="E133">
         <v>0</v>
@@ -11268,7 +10722,7 @@
         <v>3.6</v>
       </c>
       <c r="D134">
-        <v>35.200000000000003</v>
+        <v>34.353599166015087</v>
       </c>
       <c r="E134">
         <v>0</v>
@@ -11312,7 +10766,7 @@
         <v>1.28</v>
       </c>
       <c r="D135">
-        <v>24.3</v>
+        <v>23.715694878811551</v>
       </c>
       <c r="E135">
         <v>0</v>
@@ -11356,7 +10810,7 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="D136">
-        <v>27.7</v>
+        <v>27.033940252801642</v>
       </c>
       <c r="E136">
         <v>0</v>
@@ -11400,7 +10854,7 @@
         <v>0.1</v>
       </c>
       <c r="D137">
-        <v>6.8</v>
+        <v>6.6364907479801865</v>
       </c>
       <c r="E137">
         <v>0</v>
@@ -11485,7 +10939,7 @@
         <v>2.12</v>
       </c>
       <c r="D139">
-        <v>28.7</v>
+        <v>28.009894774563435</v>
       </c>
       <c r="E139">
         <v>0</v>
@@ -11529,7 +10983,7 @@
         <v>0</v>
       </c>
       <c r="D140">
-        <v>2.2000000000000002</v>
+        <v>2.1470999478759429</v>
       </c>
       <c r="E140">
         <v>0</v>
@@ -11573,7 +11027,7 @@
         <v>0</v>
       </c>
       <c r="D141">
-        <v>9</v>
+        <v>8.7835906958561303</v>
       </c>
       <c r="E141">
         <v>0</v>
@@ -11658,7 +11112,7 @@
         <v>3.75</v>
       </c>
       <c r="D143">
-        <v>24.3</v>
+        <v>23.715694878811551</v>
       </c>
       <c r="E143">
         <v>0</v>
@@ -11702,7 +11156,7 @@
         <v>0.51</v>
       </c>
       <c r="D144">
-        <v>13.6</v>
+        <v>13.272981495960373</v>
       </c>
       <c r="E144">
         <v>0</v>
@@ -11875,7 +11329,7 @@
         <v>3.26</v>
       </c>
       <c r="D148">
-        <v>28.3</v>
+        <v>27.619512965858721</v>
       </c>
       <c r="E148">
         <v>0</v>
@@ -11919,7 +11373,7 @@
         <v>0.26</v>
       </c>
       <c r="D149">
-        <v>11</v>
+        <v>10.735499739379714</v>
       </c>
       <c r="E149">
         <v>0</v>
@@ -11963,7 +11417,7 @@
         <v>0</v>
       </c>
       <c r="D150">
-        <v>11.3</v>
+        <v>11.028286095908253</v>
       </c>
       <c r="E150">
         <v>0</v>
@@ -12004,7 +11458,7 @@
         <v>0</v>
       </c>
       <c r="D151">
-        <v>86.6</v>
+        <v>84.517661584571201</v>
       </c>
       <c r="E151">
         <v>0</v>
@@ -12089,7 +11543,7 @@
         <v>3.08</v>
       </c>
       <c r="D153">
-        <v>26.5</v>
+        <v>25.862794826687495</v>
       </c>
       <c r="E153">
         <v>0</v>
@@ -12133,7 +11587,7 @@
         <v>0</v>
       </c>
       <c r="D154">
-        <v>11.9</v>
+        <v>11.613858808965327</v>
       </c>
       <c r="E154">
         <v>0</v>
@@ -12174,7 +11628,7 @@
         <v>3.74</v>
       </c>
       <c r="D155">
-        <v>88.1</v>
+        <v>85.98159336721389</v>
       </c>
       <c r="E155">
         <v>0</v>
@@ -12218,7 +11672,7 @@
         <v>0.12</v>
       </c>
       <c r="D156">
-        <v>9.9</v>
+        <v>9.6619497654417437</v>
       </c>
       <c r="E156">
         <v>0</v>
@@ -12303,7 +11757,7 @@
         <v>5.3900000000000006</v>
       </c>
       <c r="D158">
-        <v>26.6</v>
+        <v>25.960390278863674</v>
       </c>
       <c r="E158">
         <v>0</v>
@@ -12347,7 +11801,7 @@
         <v>16.29</v>
       </c>
       <c r="D159">
-        <v>63.2</v>
+        <v>61.680325775345267</v>
       </c>
       <c r="E159">
         <v>0</v>
@@ -12432,7 +11886,7 @@
         <v>2.37</v>
       </c>
       <c r="D161">
-        <v>35.700000000000003</v>
+        <v>34.841576426895983</v>
       </c>
       <c r="E161">
         <v>0</v>
@@ -12476,7 +11930,7 @@
         <v>0</v>
       </c>
       <c r="D162">
-        <v>57.4</v>
+        <v>56.01978954912687</v>
       </c>
       <c r="E162">
         <v>0</v>
@@ -12561,7 +12015,7 @@
         <v>0.69000000000000006</v>
       </c>
       <c r="D164">
-        <v>56.9</v>
+        <v>55.531812288245973</v>
       </c>
       <c r="E164">
         <v>0</v>
@@ -12605,7 +12059,7 @@
         <v>0.15</v>
       </c>
       <c r="D165">
-        <v>53</v>
+        <v>51.725589653374989</v>
       </c>
       <c r="E165">
         <v>0</v>
@@ -12693,7 +12147,7 @@
         <v>4.9099999999999993</v>
       </c>
       <c r="D167">
-        <v>25</v>
+        <v>24.398863044044806</v>
       </c>
       <c r="E167">
         <v>0</v>
@@ -12778,7 +12232,7 @@
         <v>0.75</v>
       </c>
       <c r="D169">
-        <v>33.700000000000003</v>
+        <v>32.889667383372398</v>
       </c>
       <c r="E169">
         <v>0</v>
@@ -12822,7 +12276,7 @@
         <v>13.71</v>
       </c>
       <c r="D170">
-        <v>21.1</v>
+        <v>20.592640409173818</v>
       </c>
       <c r="E170">
         <v>0</v>
@@ -12980,7 +12434,7 @@
         <v>27.47</v>
       </c>
       <c r="D174">
-        <v>33.9</v>
+        <v>33.084858287724757</v>
       </c>
       <c r="E174">
         <v>0</v>
@@ -13065,7 +12519,7 @@
         <v>3.79</v>
       </c>
       <c r="D176">
-        <v>44.7</v>
+        <v>43.625167122752117</v>
       </c>
       <c r="E176">
         <v>0</v>
@@ -13153,7 +12607,7 @@
         <v>2.25</v>
       </c>
       <c r="D178">
-        <v>33.9</v>
+        <v>33.084858287724757</v>
       </c>
       <c r="E178">
         <v>0</v>
@@ -13320,7 +12774,7 @@
         <v>34.099999999999987</v>
       </c>
       <c r="D182">
-        <v>44.8</v>
+        <v>43.722762574928289</v>
       </c>
       <c r="E182">
         <v>0</v>
@@ -13364,7 +12818,7 @@
         <v>49.92</v>
       </c>
       <c r="D183">
-        <v>54.2</v>
+        <v>52.89673507948914</v>
       </c>
       <c r="E183">
         <v>0</v>
@@ -13408,7 +12862,7 @@
         <v>8.66</v>
       </c>
       <c r="D184">
-        <v>72.5</v>
+        <v>70.756702827729939</v>
       </c>
       <c r="E184">
         <v>0</v>
@@ -13452,7 +12906,7 @@
         <v>22.33</v>
       </c>
       <c r="D185">
-        <v>23.3</v>
+        <v>22.739740357049758</v>
       </c>
       <c r="E185">
         <v>0</v>
@@ -13496,7 +12950,7 @@
         <v>33.86</v>
       </c>
       <c r="D186">
-        <v>45.7</v>
+        <v>44.60112164451391</v>
       </c>
       <c r="E186">
         <v>0</v>
@@ -13581,7 +13035,7 @@
         <v>74.95</v>
       </c>
       <c r="D188">
-        <v>71.599999999999994</v>
+        <v>69.878343758144311</v>
       </c>
       <c r="E188">
         <v>0</v>
@@ -13625,7 +13079,7 @@
         <v>10.199999999999999</v>
       </c>
       <c r="D189">
-        <v>24.1</v>
+        <v>23.520503974459192</v>
       </c>
       <c r="E189">
         <v>0</v>
@@ -13959,7 +13413,7 @@
         <v>12.47</v>
       </c>
       <c r="D197">
-        <v>29.1</v>
+        <v>28.400276583268155</v>
       </c>
       <c r="E197">
         <v>0</v>
@@ -14003,7 +13457,7 @@
         <v>6.04</v>
       </c>
       <c r="D198">
-        <v>26.5</v>
+        <v>25.862794826687495</v>
       </c>
       <c r="E198">
         <v>0</v>
@@ -14170,7 +13624,7 @@
         <v>58.36</v>
       </c>
       <c r="D202">
-        <v>69.900000000000006</v>
+        <v>68.219221071149278</v>
       </c>
       <c r="E202">
         <v>0</v>
@@ -14255,7 +13709,7 @@
         <v>7.8199999999999994</v>
       </c>
       <c r="D204">
-        <v>18.7</v>
+        <v>18.250349556945512</v>
       </c>
       <c r="E204">
         <v>0</v>
@@ -14466,7 +13920,7 @@
         <v>39.299999999999997</v>
       </c>
       <c r="D209">
-        <v>91.4</v>
+        <v>89.20224328902782</v>
       </c>
       <c r="E209">
         <v>0</v>
@@ -14551,7 +14005,7 @@
         <v>13.57</v>
       </c>
       <c r="D211">
-        <v>43.5</v>
+        <v>42.454021696637959</v>
       </c>
       <c r="E211">
         <v>0</v>
@@ -14595,7 +14049,7 @@
         <v>6.56</v>
       </c>
       <c r="D212">
-        <v>88.5</v>
+        <v>86.371975175918607</v>
       </c>
       <c r="E212">
         <v>0</v>
@@ -14639,7 +14093,7 @@
         <v>27.54</v>
       </c>
       <c r="D213">
-        <v>117.7</v>
+        <v>114.86984721136295</v>
       </c>
       <c r="E213">
         <v>0</v>
@@ -14683,7 +14137,7 @@
         <v>34.19</v>
       </c>
       <c r="D214">
-        <v>99.2</v>
+        <v>96.814688558769788</v>
       </c>
       <c r="E214">
         <v>0</v>
@@ -14768,7 +14222,7 @@
         <v>7.8800000000000008</v>
       </c>
       <c r="D216">
-        <v>22.3</v>
+        <v>21.763785835287965</v>
       </c>
       <c r="E216">
         <v>0</v>
@@ -14812,7 +14266,7 @@
         <v>21.76</v>
       </c>
       <c r="D217">
-        <v>46.6</v>
+        <v>45.479480714099516</v>
       </c>
       <c r="E217">
         <v>0</v>
@@ -14985,7 +14439,7 @@
         <v>0.74</v>
       </c>
       <c r="D221">
-        <v>55.3</v>
+        <v>53.970285053427105</v>
       </c>
       <c r="E221">
         <v>0</v>
@@ -15029,7 +14483,7 @@
         <v>6.03</v>
       </c>
       <c r="D222">
-        <v>11.8</v>
+        <v>11.516263356789148</v>
       </c>
       <c r="E222">
         <v>0</v>
@@ -15073,7 +14527,7 @@
         <v>0.73</v>
       </c>
       <c r="D223">
-        <v>26.2</v>
+        <v>25.570008470158957</v>
       </c>
       <c r="E223">
         <v>0</v>
@@ -15117,7 +14571,7 @@
         <v>3.22</v>
       </c>
       <c r="D224">
-        <v>36</v>
+        <v>35.134362783424521</v>
       </c>
       <c r="E224">
         <v>0</v>
@@ -15161,7 +14615,7 @@
         <v>42.5</v>
       </c>
       <c r="D225">
-        <v>65.900000000000006</v>
+        <v>64.315402984102107</v>
       </c>
       <c r="E225">
         <v>0</v>
@@ -15246,7 +14700,7 @@
         <v>24.98</v>
       </c>
       <c r="D227">
-        <v>57.3</v>
+        <v>55.92219409695069</v>
       </c>
       <c r="E227">
         <v>0</v>
@@ -15413,7 +14867,7 @@
         <v>21.72</v>
       </c>
       <c r="D231">
-        <v>33.5</v>
+        <v>32.69447647902004</v>
       </c>
       <c r="E231">
         <v>0</v>
@@ -15539,7 +14993,7 @@
         <v>5.57</v>
       </c>
       <c r="D234">
-        <v>3.4</v>
+        <v>3.3182453739900932</v>
       </c>
       <c r="E234">
         <v>0</v>
@@ -15624,7 +15078,7 @@
         <v>10</v>
       </c>
       <c r="D236">
-        <v>71.400000000000006</v>
+        <v>69.683152853791967</v>
       </c>
       <c r="E236">
         <v>0</v>
@@ -15794,7 +15248,7 @@
         <v>38.42</v>
       </c>
       <c r="D240">
-        <v>22.2</v>
+        <v>21.666190383111786</v>
       </c>
       <c r="E240">
         <v>0</v>
@@ -15838,7 +15292,7 @@
         <v>33.369999999999997</v>
       </c>
       <c r="D241">
-        <v>39</v>
+        <v>38.062226348709899</v>
       </c>
       <c r="E241">
         <v>0</v>
@@ -15882,7 +15336,7 @@
         <v>31.38</v>
       </c>
       <c r="D242">
-        <v>52.5</v>
+        <v>51.237612392494093</v>
       </c>
       <c r="E242">
         <v>0</v>
@@ -15926,7 +15380,7 @@
         <v>23.49</v>
       </c>
       <c r="D243">
-        <v>52.8</v>
+        <v>51.530398749022623</v>
       </c>
       <c r="E243">
         <v>0</v>
@@ -15970,7 +15424,7 @@
         <v>7.17</v>
       </c>
       <c r="D244">
-        <v>44.5</v>
+        <v>43.429976218399752</v>
       </c>
       <c r="E244">
         <v>0</v>
@@ -16055,7 +15509,7 @@
         <v>7.67</v>
       </c>
       <c r="D246">
-        <v>57.4</v>
+        <v>56.01978954912687</v>
       </c>
       <c r="E246">
         <v>0</v>
@@ -16181,7 +15635,7 @@
         <v>0</v>
       </c>
       <c r="D249">
-        <v>61.5</v>
+        <v>60.021203088350219</v>
       </c>
       <c r="E249">
         <v>0</v>
@@ -16263,7 +15717,7 @@
         <v>24.68</v>
       </c>
       <c r="D251">
-        <v>65.599999999999994</v>
+        <v>64.022616627573569</v>
       </c>
       <c r="E251">
         <v>0</v>
@@ -16307,7 +15761,7 @@
         <v>31.65</v>
       </c>
       <c r="D252">
-        <v>55.8</v>
+        <v>54.458262314308001</v>
       </c>
       <c r="E252">
         <v>0</v>
@@ -16351,7 +15805,7 @@
         <v>12.44</v>
       </c>
       <c r="D253">
-        <v>29.8</v>
+        <v>29.083444748501407</v>
       </c>
       <c r="E253">
         <v>0</v>
@@ -16395,7 +15849,7 @@
         <v>14.17</v>
       </c>
       <c r="D254">
-        <v>32.9</v>
+        <v>32.108903765962964</v>
       </c>
       <c r="E254">
         <v>0</v>
@@ -16439,7 +15893,7 @@
         <v>28.58</v>
       </c>
       <c r="D255">
-        <v>38.9</v>
+        <v>37.964630896533713</v>
       </c>
       <c r="E255">
         <v>0</v>
@@ -16650,7 +16104,7 @@
         <v>0</v>
       </c>
       <c r="D260">
-        <v>26.7</v>
+        <v>26.057985731039849</v>
       </c>
       <c r="E260">
         <v>0</v>
@@ -16694,7 +16148,7 @@
         <v>0</v>
       </c>
       <c r="D261">
-        <v>56.2</v>
+        <v>54.848644123012726</v>
       </c>
       <c r="E261">
         <v>0</v>
@@ -16735,7 +16189,7 @@
         <v>25.04</v>
       </c>
       <c r="D262">
-        <v>11.2</v>
+        <v>10.930690643732072</v>
       </c>
       <c r="E262">
         <v>0</v>
@@ -16820,7 +16274,7 @@
         <v>11.84</v>
       </c>
       <c r="D264">
-        <v>28.3</v>
+        <v>27.619512965858721</v>
       </c>
       <c r="E264">
         <v>0</v>
@@ -16864,7 +16318,7 @@
         <v>0</v>
       </c>
       <c r="D265">
-        <v>15.7</v>
+        <v>15.322485991660137</v>
       </c>
       <c r="E265">
         <v>0</v>
@@ -16905,7 +16359,7 @@
         <v>16.28</v>
       </c>
       <c r="D266">
-        <v>71.3</v>
+        <v>69.585557401615787</v>
       </c>
       <c r="E266">
         <v>0</v>
@@ -16949,7 +16403,7 @@
         <v>25.35</v>
       </c>
       <c r="D267">
-        <v>47.1</v>
+        <v>45.967457974980412</v>
       </c>
       <c r="E267">
         <v>0</v>
@@ -16993,7 +16447,7 @@
         <v>0.16</v>
       </c>
       <c r="D268">
-        <v>3.4</v>
+        <v>3.3182453739900932</v>
       </c>
       <c r="E268">
         <v>0</v>
@@ -17078,7 +16532,7 @@
         <v>33.6</v>
       </c>
       <c r="D270">
-        <v>107.1</v>
+        <v>104.52472928068794</v>
       </c>
       <c r="E270">
         <v>0</v>
@@ -17122,7 +16576,7 @@
         <v>0</v>
       </c>
       <c r="D271">
-        <v>23.3</v>
+        <v>22.739740357049758</v>
       </c>
       <c r="E271">
         <v>0</v>
@@ -17163,7 +16617,7 @@
         <v>0</v>
       </c>
       <c r="D272">
-        <v>15.3</v>
+        <v>14.932104182955422</v>
       </c>
       <c r="E272">
         <v>0</v>
@@ -17207,7 +16661,7 @@
         <v>18.61</v>
       </c>
       <c r="D273">
-        <v>35.6</v>
+        <v>34.743980974719804</v>
       </c>
       <c r="E273">
         <v>0</v>
@@ -17251,7 +16705,7 @@
         <v>20.04</v>
       </c>
       <c r="D274">
-        <v>43.1</v>
+        <v>42.063639887933249</v>
       </c>
       <c r="E274">
         <v>0</v>
@@ -17295,7 +16749,7 @@
         <v>20.36</v>
       </c>
       <c r="D275">
-        <v>59.1</v>
+        <v>57.678912236121924</v>
       </c>
       <c r="E275">
         <v>0</v>
@@ -17465,7 +16919,7 @@
         <v>44.48</v>
       </c>
       <c r="D279">
-        <v>48</v>
+        <v>46.845817044566026</v>
       </c>
       <c r="E279">
         <v>0</v>
@@ -17509,7 +16963,7 @@
         <v>14.81</v>
       </c>
       <c r="D280">
-        <v>45.8</v>
+        <v>44.698717096690082</v>
       </c>
       <c r="E280">
         <v>0</v>
@@ -17553,7 +17007,7 @@
         <v>12.57</v>
       </c>
       <c r="D281">
-        <v>35.4</v>
+        <v>34.548790070367446</v>
       </c>
       <c r="E281">
         <v>0</v>
@@ -17597,7 +17051,7 @@
         <v>12.48</v>
       </c>
       <c r="D282">
-        <v>28.7</v>
+        <v>28.009894774563435</v>
       </c>
       <c r="E282">
         <v>0</v>
@@ -18095,7 +17549,7 @@
         <v>11.24</v>
       </c>
       <c r="D294">
-        <v>15.5</v>
+        <v>15.127295087307779</v>
       </c>
       <c r="E294">
         <v>0</v>
@@ -18180,7 +17634,7 @@
         <v>18</v>
       </c>
       <c r="D296">
-        <v>42.3</v>
+        <v>41.282876270523808</v>
       </c>
       <c r="E296">
         <v>0</v>
@@ -18224,7 +17678,7 @@
         <v>15.32</v>
       </c>
       <c r="D297">
-        <v>25.6</v>
+        <v>24.984435757101881</v>
       </c>
       <c r="E297">
         <v>0</v>
@@ -18350,7 +17804,7 @@
         <v>26.78</v>
       </c>
       <c r="D300">
-        <v>35.700000000000003</v>
+        <v>34.841576426895983</v>
       </c>
       <c r="E300">
         <v>0</v>
@@ -18394,7 +17848,7 @@
         <v>21.37</v>
       </c>
       <c r="D301">
-        <v>25.3</v>
+        <v>24.691649400573343</v>
       </c>
       <c r="E301">
         <v>0</v>
@@ -18437,6 +17891,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AE439"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="4" max="4" width="18.33203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
@@ -31871,7 +31328,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="353" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A353">
         <v>294</v>
       </c>
@@ -31909,7 +31366,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="354" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A354">
         <v>298</v>
       </c>
@@ -31947,7 +31404,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="355" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A355">
         <v>311</v>
       </c>
@@ -31985,7 +31442,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="356" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A356">
         <v>305</v>
       </c>
@@ -32023,7 +31480,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="357" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A357">
         <v>305</v>
       </c>
@@ -32061,7 +31518,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="358" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A358">
         <v>321</v>
       </c>
@@ -32099,7 +31556,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="359" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A359">
         <v>326</v>
       </c>
@@ -32137,7 +31594,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="360" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A360">
         <v>58</v>
       </c>
@@ -32145,61 +31602,16 @@
         <v>56</v>
       </c>
       <c r="C360" t="s">
+        <v>1593</v>
+      </c>
+      <c r="D360">
+        <v>10000</v>
+      </c>
+      <c r="L360" t="s">
         <v>1592</v>
       </c>
-      <c r="F360" t="s">
-        <v>1593</v>
-      </c>
-      <c r="L360" t="s">
-        <v>1593</v>
-      </c>
-      <c r="M360" t="s">
-        <v>1594</v>
-      </c>
-      <c r="N360" t="s">
-        <v>1595</v>
-      </c>
-      <c r="O360" t="s">
-        <v>1596</v>
-      </c>
-      <c r="P360" t="s">
-        <v>1597</v>
-      </c>
-      <c r="Q360" t="s">
-        <v>1598</v>
-      </c>
-      <c r="R360" t="s">
-        <v>1599</v>
-      </c>
-      <c r="S360" t="s">
-        <v>699</v>
-      </c>
-      <c r="T360" t="s">
-        <v>1600</v>
-      </c>
-      <c r="U360">
-        <v>1</v>
-      </c>
-      <c r="V360">
-        <v>1</v>
-      </c>
-      <c r="W360">
-        <v>1</v>
-      </c>
-      <c r="X360">
-        <v>1</v>
-      </c>
-      <c r="Y360" t="s">
-        <v>619</v>
-      </c>
-      <c r="Z360">
-        <v>0</v>
-      </c>
-      <c r="AA360" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="361" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="361" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A361">
         <v>58</v>
       </c>
@@ -32207,61 +31619,16 @@
         <v>57</v>
       </c>
       <c r="C361" t="s">
+        <v>1594</v>
+      </c>
+      <c r="D361">
+        <v>10000</v>
+      </c>
+      <c r="L361" t="s">
         <v>1592</v>
       </c>
-      <c r="F361" t="s">
-        <v>1593</v>
-      </c>
-      <c r="L361" t="s">
-        <v>1593</v>
-      </c>
-      <c r="M361" t="s">
-        <v>1602</v>
-      </c>
-      <c r="N361" t="s">
-        <v>1595</v>
-      </c>
-      <c r="O361" t="s">
-        <v>1603</v>
-      </c>
-      <c r="P361" t="s">
-        <v>1604</v>
-      </c>
-      <c r="Q361" t="s">
-        <v>638</v>
-      </c>
-      <c r="R361" t="s">
-        <v>1605</v>
-      </c>
-      <c r="S361" t="s">
-        <v>823</v>
-      </c>
-      <c r="T361" t="s">
-        <v>1606</v>
-      </c>
-      <c r="U361">
-        <v>1</v>
-      </c>
-      <c r="V361">
-        <v>1</v>
-      </c>
-      <c r="W361">
-        <v>1</v>
-      </c>
-      <c r="X361">
-        <v>1</v>
-      </c>
-      <c r="Y361" t="s">
-        <v>619</v>
-      </c>
-      <c r="Z361">
-        <v>0</v>
-      </c>
-      <c r="AA361" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="362" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="362" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A362">
         <v>61</v>
       </c>
@@ -32269,61 +31636,16 @@
         <v>59</v>
       </c>
       <c r="C362" t="s">
+        <v>1595</v>
+      </c>
+      <c r="D362">
+        <v>10000</v>
+      </c>
+      <c r="L362" t="s">
         <v>1592</v>
       </c>
-      <c r="F362" t="s">
-        <v>1593</v>
-      </c>
-      <c r="L362" t="s">
-        <v>1593</v>
-      </c>
-      <c r="M362" t="s">
-        <v>1607</v>
-      </c>
-      <c r="N362" t="s">
-        <v>1608</v>
-      </c>
-      <c r="O362" t="s">
-        <v>1609</v>
-      </c>
-      <c r="P362" t="s">
-        <v>1610</v>
-      </c>
-      <c r="Q362" t="s">
-        <v>1468</v>
-      </c>
-      <c r="R362" t="s">
-        <v>1611</v>
-      </c>
-      <c r="S362" t="s">
-        <v>1612</v>
-      </c>
-      <c r="T362" t="s">
-        <v>1613</v>
-      </c>
-      <c r="U362">
-        <v>1</v>
-      </c>
-      <c r="V362">
-        <v>1</v>
-      </c>
-      <c r="W362">
-        <v>1</v>
-      </c>
-      <c r="X362">
-        <v>1</v>
-      </c>
-      <c r="Y362" t="s">
-        <v>619</v>
-      </c>
-      <c r="Z362">
-        <v>0</v>
-      </c>
-      <c r="AA362" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="363" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="363" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A363">
         <v>62</v>
       </c>
@@ -32331,73 +31653,16 @@
         <v>61</v>
       </c>
       <c r="C363" t="s">
+        <v>1596</v>
+      </c>
+      <c r="D363">
+        <v>10000</v>
+      </c>
+      <c r="L363" t="s">
         <v>1592</v>
       </c>
-      <c r="F363" t="s">
-        <v>1593</v>
-      </c>
-      <c r="L363" t="s">
-        <v>1593</v>
-      </c>
-      <c r="M363" t="s">
-        <v>1614</v>
-      </c>
-      <c r="N363" t="s">
-        <v>1615</v>
-      </c>
-      <c r="O363" t="s">
-        <v>1616</v>
-      </c>
-      <c r="P363" t="s">
-        <v>1617</v>
-      </c>
-      <c r="Q363" t="s">
-        <v>1618</v>
-      </c>
-      <c r="R363" t="s">
-        <v>1619</v>
-      </c>
-      <c r="S363" t="s">
-        <v>913</v>
-      </c>
-      <c r="T363" t="s">
-        <v>1620</v>
-      </c>
-      <c r="U363">
-        <v>1</v>
-      </c>
-      <c r="V363">
-        <v>27</v>
-      </c>
-      <c r="W363">
-        <v>14</v>
-      </c>
-      <c r="X363">
-        <v>14</v>
-      </c>
-      <c r="Y363" t="s">
-        <v>815</v>
-      </c>
-      <c r="Z363">
-        <v>-180</v>
-      </c>
-      <c r="AA363" t="s">
-        <v>1621</v>
-      </c>
-      <c r="AB363" t="s">
-        <v>1622</v>
-      </c>
-      <c r="AC363" t="s">
-        <v>1249</v>
-      </c>
-      <c r="AD363" t="s">
-        <v>885</v>
-      </c>
-      <c r="AE363">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="364" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="364" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A364">
         <v>63</v>
       </c>
@@ -32405,61 +31670,16 @@
         <v>60</v>
       </c>
       <c r="C364" t="s">
+        <v>1597</v>
+      </c>
+      <c r="D364">
+        <v>10000</v>
+      </c>
+      <c r="L364" t="s">
         <v>1592</v>
       </c>
-      <c r="F364" t="s">
-        <v>1593</v>
-      </c>
-      <c r="L364" t="s">
-        <v>1593</v>
-      </c>
-      <c r="M364" t="s">
-        <v>1623</v>
-      </c>
-      <c r="N364" t="s">
-        <v>1624</v>
-      </c>
-      <c r="O364" t="s">
-        <v>1625</v>
-      </c>
-      <c r="P364" t="s">
-        <v>1626</v>
-      </c>
-      <c r="Q364" t="s">
-        <v>1627</v>
-      </c>
-      <c r="R364" t="s">
-        <v>1628</v>
-      </c>
-      <c r="S364" t="s">
-        <v>628</v>
-      </c>
-      <c r="T364" t="s">
-        <v>1629</v>
-      </c>
-      <c r="U364">
-        <v>1</v>
-      </c>
-      <c r="V364">
-        <v>1</v>
-      </c>
-      <c r="W364">
-        <v>1</v>
-      </c>
-      <c r="X364">
-        <v>1</v>
-      </c>
-      <c r="Y364" t="s">
-        <v>619</v>
-      </c>
-      <c r="Z364">
-        <v>0</v>
-      </c>
-      <c r="AA364" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="365" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="365" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A365">
         <v>63</v>
       </c>
@@ -32467,61 +31687,16 @@
         <v>62</v>
       </c>
       <c r="C365" t="s">
+        <v>1598</v>
+      </c>
+      <c r="D365">
+        <v>10000</v>
+      </c>
+      <c r="L365" t="s">
         <v>1592</v>
       </c>
-      <c r="F365" t="s">
-        <v>1593</v>
-      </c>
-      <c r="L365" t="s">
-        <v>1593</v>
-      </c>
-      <c r="M365" t="s">
-        <v>1630</v>
-      </c>
-      <c r="N365" t="s">
-        <v>1615</v>
-      </c>
-      <c r="O365" t="s">
-        <v>1615</v>
-      </c>
-      <c r="P365" t="s">
-        <v>1617</v>
-      </c>
-      <c r="Q365" t="s">
-        <v>913</v>
-      </c>
-      <c r="R365" t="s">
-        <v>1631</v>
-      </c>
-      <c r="S365" t="s">
-        <v>619</v>
-      </c>
-      <c r="T365" t="s">
-        <v>1632</v>
-      </c>
-      <c r="U365">
-        <v>1</v>
-      </c>
-      <c r="V365">
-        <v>21</v>
-      </c>
-      <c r="W365">
-        <v>1</v>
-      </c>
-      <c r="X365">
-        <v>2</v>
-      </c>
-      <c r="Y365" t="s">
-        <v>1100</v>
-      </c>
-      <c r="Z365">
-        <v>-179</v>
-      </c>
-      <c r="AA365" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="366" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="366" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A366">
         <v>69</v>
       </c>
@@ -32529,61 +31704,16 @@
         <v>68</v>
       </c>
       <c r="C366" t="s">
+        <v>1599</v>
+      </c>
+      <c r="D366">
+        <v>10000</v>
+      </c>
+      <c r="L366" t="s">
         <v>1592</v>
       </c>
-      <c r="F366" t="s">
-        <v>1593</v>
-      </c>
-      <c r="L366" t="s">
-        <v>1593</v>
-      </c>
-      <c r="M366" t="s">
-        <v>1633</v>
-      </c>
-      <c r="N366" t="s">
-        <v>1616</v>
-      </c>
-      <c r="O366" t="s">
-        <v>1616</v>
-      </c>
-      <c r="P366" t="s">
-        <v>1634</v>
-      </c>
-      <c r="Q366" t="s">
-        <v>907</v>
-      </c>
-      <c r="R366" t="s">
-        <v>1635</v>
-      </c>
-      <c r="S366" t="s">
-        <v>854</v>
-      </c>
-      <c r="T366" t="s">
-        <v>1636</v>
-      </c>
-      <c r="U366">
-        <v>-8</v>
-      </c>
-      <c r="V366">
-        <v>8</v>
-      </c>
-      <c r="W366">
-        <v>0</v>
-      </c>
-      <c r="X366">
-        <v>0</v>
-      </c>
-      <c r="Y366" t="s">
-        <v>619</v>
-      </c>
-      <c r="Z366">
-        <v>1</v>
-      </c>
-      <c r="AA366" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="367" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="367" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A367">
         <v>68</v>
       </c>
@@ -32591,61 +31721,16 @@
         <v>66</v>
       </c>
       <c r="C367" t="s">
+        <v>1600</v>
+      </c>
+      <c r="D367">
+        <v>10000</v>
+      </c>
+      <c r="L367" t="s">
         <v>1592</v>
       </c>
-      <c r="F367" t="s">
-        <v>1593</v>
-      </c>
-      <c r="L367" t="s">
-        <v>1593</v>
-      </c>
-      <c r="M367" t="s">
-        <v>1637</v>
-      </c>
-      <c r="N367" t="s">
-        <v>1595</v>
-      </c>
-      <c r="O367" t="s">
-        <v>1603</v>
-      </c>
-      <c r="P367" t="s">
-        <v>1604</v>
-      </c>
-      <c r="Q367" t="s">
-        <v>638</v>
-      </c>
-      <c r="R367" t="s">
-        <v>1605</v>
-      </c>
-      <c r="S367" t="s">
-        <v>823</v>
-      </c>
-      <c r="T367" t="s">
-        <v>1606</v>
-      </c>
-      <c r="U367">
-        <v>1</v>
-      </c>
-      <c r="V367">
-        <v>1</v>
-      </c>
-      <c r="W367">
-        <v>1</v>
-      </c>
-      <c r="X367">
-        <v>1</v>
-      </c>
-      <c r="Y367" t="s">
-        <v>619</v>
-      </c>
-      <c r="Z367">
-        <v>0</v>
-      </c>
-      <c r="AA367" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="368" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="368" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A368">
         <v>70</v>
       </c>
@@ -32653,61 +31738,16 @@
         <v>67</v>
       </c>
       <c r="C368" t="s">
+        <v>1601</v>
+      </c>
+      <c r="D368">
+        <v>10000</v>
+      </c>
+      <c r="L368" t="s">
         <v>1592</v>
       </c>
-      <c r="F368" t="s">
-        <v>1593</v>
-      </c>
-      <c r="L368" t="s">
-        <v>1593</v>
-      </c>
-      <c r="M368" t="s">
-        <v>1638</v>
-      </c>
-      <c r="N368" t="s">
-        <v>1624</v>
-      </c>
-      <c r="O368" t="s">
-        <v>1639</v>
-      </c>
-      <c r="P368" t="s">
-        <v>1640</v>
-      </c>
-      <c r="Q368" t="s">
-        <v>1641</v>
-      </c>
-      <c r="R368" t="s">
-        <v>1642</v>
-      </c>
-      <c r="S368" t="s">
-        <v>839</v>
-      </c>
-      <c r="T368" t="s">
-        <v>1643</v>
-      </c>
-      <c r="U368">
-        <v>1</v>
-      </c>
-      <c r="V368">
-        <v>1</v>
-      </c>
-      <c r="W368">
-        <v>1</v>
-      </c>
-      <c r="X368">
-        <v>1</v>
-      </c>
-      <c r="Y368" t="s">
-        <v>619</v>
-      </c>
-      <c r="Z368">
-        <v>0</v>
-      </c>
-      <c r="AA368" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="369" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="369" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A369">
         <v>70</v>
       </c>
@@ -32715,73 +31755,16 @@
         <v>69</v>
       </c>
       <c r="C369" t="s">
+        <v>1602</v>
+      </c>
+      <c r="D369">
+        <v>10000</v>
+      </c>
+      <c r="L369" t="s">
         <v>1592</v>
       </c>
-      <c r="F369" t="s">
-        <v>1593</v>
-      </c>
-      <c r="L369" t="s">
-        <v>1593</v>
-      </c>
-      <c r="M369" t="s">
-        <v>1644</v>
-      </c>
-      <c r="N369" t="s">
-        <v>1615</v>
-      </c>
-      <c r="O369" t="s">
-        <v>1616</v>
-      </c>
-      <c r="P369" t="s">
-        <v>1643</v>
-      </c>
-      <c r="Q369" t="s">
-        <v>1645</v>
-      </c>
-      <c r="R369" t="s">
-        <v>1624</v>
-      </c>
-      <c r="S369" t="s">
-        <v>913</v>
-      </c>
-      <c r="T369" t="s">
-        <v>1646</v>
-      </c>
-      <c r="U369">
-        <v>1</v>
-      </c>
-      <c r="V369">
-        <v>17</v>
-      </c>
-      <c r="W369">
-        <v>9</v>
-      </c>
-      <c r="X369">
-        <v>10</v>
-      </c>
-      <c r="Y369" t="s">
-        <v>620</v>
-      </c>
-      <c r="Z369">
-        <v>-180</v>
-      </c>
-      <c r="AA369" t="s">
-        <v>1621</v>
-      </c>
-      <c r="AB369" t="s">
-        <v>1622</v>
-      </c>
-      <c r="AC369" t="s">
-        <v>1249</v>
-      </c>
-      <c r="AD369" t="s">
-        <v>885</v>
-      </c>
-      <c r="AE369">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="370" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="370" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A370">
         <v>76</v>
       </c>
@@ -32789,61 +31772,16 @@
         <v>77</v>
       </c>
       <c r="C370" t="s">
+        <v>1603</v>
+      </c>
+      <c r="D370">
+        <v>10000</v>
+      </c>
+      <c r="L370" t="s">
         <v>1592</v>
       </c>
-      <c r="F370" t="s">
-        <v>1593</v>
-      </c>
-      <c r="L370" t="s">
-        <v>1593</v>
-      </c>
-      <c r="M370" t="s">
-        <v>1647</v>
-      </c>
-      <c r="N370" t="s">
-        <v>1648</v>
-      </c>
-      <c r="O370" t="s">
-        <v>1648</v>
-      </c>
-      <c r="P370" t="s">
-        <v>1605</v>
-      </c>
-      <c r="Q370" t="s">
-        <v>1309</v>
-      </c>
-      <c r="R370" t="s">
-        <v>1632</v>
-      </c>
-      <c r="S370" t="s">
-        <v>619</v>
-      </c>
-      <c r="T370" t="s">
-        <v>1632</v>
-      </c>
-      <c r="U370">
-        <v>-10</v>
-      </c>
-      <c r="V370">
-        <v>10</v>
-      </c>
-      <c r="W370">
-        <v>0</v>
-      </c>
-      <c r="X370">
-        <v>0</v>
-      </c>
-      <c r="Y370" t="s">
-        <v>786</v>
-      </c>
-      <c r="Z370">
-        <v>90</v>
-      </c>
-      <c r="AA370" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="371" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="371" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A371">
         <v>78</v>
       </c>
@@ -32851,73 +31789,16 @@
         <v>74</v>
       </c>
       <c r="C371" t="s">
+        <v>1604</v>
+      </c>
+      <c r="D371">
+        <v>10000</v>
+      </c>
+      <c r="L371" t="s">
         <v>1592</v>
       </c>
-      <c r="F371" t="s">
-        <v>1593</v>
-      </c>
-      <c r="L371" t="s">
-        <v>1593</v>
-      </c>
-      <c r="M371" t="s">
-        <v>1649</v>
-      </c>
-      <c r="N371" t="s">
-        <v>1650</v>
-      </c>
-      <c r="O371" t="s">
-        <v>1651</v>
-      </c>
-      <c r="P371" t="s">
-        <v>1643</v>
-      </c>
-      <c r="Q371" t="s">
-        <v>1233</v>
-      </c>
-      <c r="R371" t="s">
-        <v>1652</v>
-      </c>
-      <c r="S371" t="s">
-        <v>1095</v>
-      </c>
-      <c r="T371" t="s">
-        <v>1653</v>
-      </c>
-      <c r="U371">
-        <v>1</v>
-      </c>
-      <c r="V371">
-        <v>21</v>
-      </c>
-      <c r="W371">
-        <v>11</v>
-      </c>
-      <c r="X371">
-        <v>11</v>
-      </c>
-      <c r="Y371" t="s">
-        <v>1193</v>
-      </c>
-      <c r="Z371">
-        <v>0</v>
-      </c>
-      <c r="AA371" t="s">
-        <v>1621</v>
-      </c>
-      <c r="AB371" t="s">
-        <v>1622</v>
-      </c>
-      <c r="AC371" t="s">
-        <v>1654</v>
-      </c>
-      <c r="AD371" t="s">
-        <v>972</v>
-      </c>
-      <c r="AE371">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="372" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="372" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A372">
         <v>78</v>
       </c>
@@ -32925,73 +31806,16 @@
         <v>75</v>
       </c>
       <c r="C372" t="s">
+        <v>1605</v>
+      </c>
+      <c r="D372">
+        <v>10000</v>
+      </c>
+      <c r="L372" t="s">
         <v>1592</v>
       </c>
-      <c r="F372" t="s">
-        <v>1593</v>
-      </c>
-      <c r="L372" t="s">
-        <v>1593</v>
-      </c>
-      <c r="M372" t="s">
-        <v>1655</v>
-      </c>
-      <c r="N372" t="s">
-        <v>1615</v>
-      </c>
-      <c r="O372" t="s">
-        <v>1616</v>
-      </c>
-      <c r="P372" t="s">
-        <v>1615</v>
-      </c>
-      <c r="Q372" t="s">
-        <v>1656</v>
-      </c>
-      <c r="R372" t="s">
-        <v>1657</v>
-      </c>
-      <c r="S372" t="s">
-        <v>628</v>
-      </c>
-      <c r="T372" t="s">
-        <v>1658</v>
-      </c>
-      <c r="U372">
-        <v>1</v>
-      </c>
-      <c r="V372">
-        <v>17</v>
-      </c>
-      <c r="W372">
-        <v>9</v>
-      </c>
-      <c r="X372">
-        <v>9</v>
-      </c>
-      <c r="Y372" t="s">
-        <v>620</v>
-      </c>
-      <c r="Z372">
-        <v>-180</v>
-      </c>
-      <c r="AA372" t="s">
-        <v>1621</v>
-      </c>
-      <c r="AB372" t="s">
-        <v>1622</v>
-      </c>
-      <c r="AC372" t="s">
-        <v>1249</v>
-      </c>
-      <c r="AD372" t="s">
-        <v>885</v>
-      </c>
-      <c r="AE372">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="373" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="373" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A373">
         <v>78</v>
       </c>
@@ -32999,73 +31823,16 @@
         <v>75</v>
       </c>
       <c r="C373" t="s">
+        <v>1606</v>
+      </c>
+      <c r="D373">
+        <v>10000</v>
+      </c>
+      <c r="L373" t="s">
         <v>1592</v>
       </c>
-      <c r="F373" t="s">
-        <v>1593</v>
-      </c>
-      <c r="L373" t="s">
-        <v>1593</v>
-      </c>
-      <c r="M373" t="s">
-        <v>1659</v>
-      </c>
-      <c r="N373" t="s">
-        <v>1660</v>
-      </c>
-      <c r="O373" t="s">
-        <v>1661</v>
-      </c>
-      <c r="P373" t="s">
-        <v>1662</v>
-      </c>
-      <c r="Q373" t="s">
-        <v>1663</v>
-      </c>
-      <c r="R373" t="s">
-        <v>1664</v>
-      </c>
-      <c r="S373" t="s">
-        <v>907</v>
-      </c>
-      <c r="T373" t="s">
-        <v>1665</v>
-      </c>
-      <c r="U373">
-        <v>1</v>
-      </c>
-      <c r="V373">
-        <v>27</v>
-      </c>
-      <c r="W373">
-        <v>14</v>
-      </c>
-      <c r="X373">
-        <v>17</v>
-      </c>
-      <c r="Y373" t="s">
-        <v>1150</v>
-      </c>
-      <c r="Z373">
-        <v>-180</v>
-      </c>
-      <c r="AA373" t="s">
-        <v>1621</v>
-      </c>
-      <c r="AB373" t="s">
-        <v>1622</v>
-      </c>
-      <c r="AC373" t="s">
-        <v>1249</v>
-      </c>
-      <c r="AD373" t="s">
-        <v>885</v>
-      </c>
-      <c r="AE373">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="374" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="374" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A374">
         <v>78</v>
       </c>
@@ -33073,73 +31840,16 @@
         <v>76</v>
       </c>
       <c r="C374" t="s">
+        <v>1607</v>
+      </c>
+      <c r="D374">
+        <v>10000</v>
+      </c>
+      <c r="L374" t="s">
         <v>1592</v>
       </c>
-      <c r="F374" t="s">
-        <v>1593</v>
-      </c>
-      <c r="L374" t="s">
-        <v>1593</v>
-      </c>
-      <c r="M374" t="s">
-        <v>1666</v>
-      </c>
-      <c r="N374" t="s">
-        <v>1667</v>
-      </c>
-      <c r="O374" t="s">
-        <v>1629</v>
-      </c>
-      <c r="P374" t="s">
-        <v>1617</v>
-      </c>
-      <c r="Q374" t="s">
-        <v>1668</v>
-      </c>
-      <c r="R374" t="s">
-        <v>1617</v>
-      </c>
-      <c r="S374" t="s">
-        <v>615</v>
-      </c>
-      <c r="T374" t="s">
-        <v>1669</v>
-      </c>
-      <c r="U374">
-        <v>1</v>
-      </c>
-      <c r="V374">
-        <v>21</v>
-      </c>
-      <c r="W374">
-        <v>11</v>
-      </c>
-      <c r="X374">
-        <v>11</v>
-      </c>
-      <c r="Y374" t="s">
-        <v>620</v>
-      </c>
-      <c r="Z374">
-        <v>0</v>
-      </c>
-      <c r="AA374" t="s">
-        <v>1621</v>
-      </c>
-      <c r="AB374" t="s">
-        <v>1622</v>
-      </c>
-      <c r="AC374" t="s">
-        <v>1654</v>
-      </c>
-      <c r="AD374" t="s">
-        <v>1150</v>
-      </c>
-      <c r="AE374">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="375" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="375" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A375">
         <v>99</v>
       </c>
@@ -33147,61 +31857,16 @@
         <v>98</v>
       </c>
       <c r="C375" t="s">
+        <v>1608</v>
+      </c>
+      <c r="D375">
+        <v>10000</v>
+      </c>
+      <c r="L375" t="s">
         <v>1592</v>
       </c>
-      <c r="F375" t="s">
-        <v>1593</v>
-      </c>
-      <c r="L375" t="s">
-        <v>1593</v>
-      </c>
-      <c r="M375" t="s">
-        <v>1670</v>
-      </c>
-      <c r="N375" t="s">
-        <v>1616</v>
-      </c>
-      <c r="O375" t="s">
-        <v>1616</v>
-      </c>
-      <c r="P375" t="s">
-        <v>1671</v>
-      </c>
-      <c r="Q375" t="s">
-        <v>743</v>
-      </c>
-      <c r="R375" t="s">
-        <v>1672</v>
-      </c>
-      <c r="S375" t="s">
-        <v>854</v>
-      </c>
-      <c r="T375" t="s">
-        <v>1673</v>
-      </c>
-      <c r="U375">
-        <v>-8</v>
-      </c>
-      <c r="V375">
-        <v>8</v>
-      </c>
-      <c r="W375">
-        <v>0</v>
-      </c>
-      <c r="X375">
-        <v>0</v>
-      </c>
-      <c r="Y375" t="s">
-        <v>619</v>
-      </c>
-      <c r="Z375">
-        <v>1</v>
-      </c>
-      <c r="AA375" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="376" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="376" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A376">
         <v>100</v>
       </c>
@@ -33209,73 +31874,16 @@
         <v>99</v>
       </c>
       <c r="C376" t="s">
+        <v>1609</v>
+      </c>
+      <c r="D376">
+        <v>10000</v>
+      </c>
+      <c r="L376" t="s">
         <v>1592</v>
       </c>
-      <c r="F376" t="s">
-        <v>1593</v>
-      </c>
-      <c r="L376" t="s">
-        <v>1593</v>
-      </c>
-      <c r="M376" t="s">
-        <v>1674</v>
-      </c>
-      <c r="N376" t="s">
-        <v>1615</v>
-      </c>
-      <c r="O376" t="s">
-        <v>1616</v>
-      </c>
-      <c r="P376" t="s">
-        <v>1615</v>
-      </c>
-      <c r="Q376" t="s">
-        <v>1656</v>
-      </c>
-      <c r="R376" t="s">
-        <v>1657</v>
-      </c>
-      <c r="S376" t="s">
-        <v>628</v>
-      </c>
-      <c r="T376" t="s">
-        <v>1658</v>
-      </c>
-      <c r="U376">
-        <v>1</v>
-      </c>
-      <c r="V376">
-        <v>17</v>
-      </c>
-      <c r="W376">
-        <v>9</v>
-      </c>
-      <c r="X376">
-        <v>9</v>
-      </c>
-      <c r="Y376" t="s">
-        <v>620</v>
-      </c>
-      <c r="Z376">
-        <v>-180</v>
-      </c>
-      <c r="AA376" t="s">
-        <v>1621</v>
-      </c>
-      <c r="AB376" t="s">
-        <v>1622</v>
-      </c>
-      <c r="AC376" t="s">
-        <v>1249</v>
-      </c>
-      <c r="AD376" t="s">
-        <v>885</v>
-      </c>
-      <c r="AE376">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="377" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="377" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A377">
         <v>103</v>
       </c>
@@ -33283,73 +31891,16 @@
         <v>102</v>
       </c>
       <c r="C377" t="s">
+        <v>1610</v>
+      </c>
+      <c r="D377">
+        <v>10000</v>
+      </c>
+      <c r="L377" t="s">
         <v>1592</v>
       </c>
-      <c r="F377" t="s">
-        <v>1593</v>
-      </c>
-      <c r="L377" t="s">
-        <v>1593</v>
-      </c>
-      <c r="M377" t="s">
-        <v>1675</v>
-      </c>
-      <c r="N377" t="s">
-        <v>1615</v>
-      </c>
-      <c r="O377" t="s">
-        <v>1616</v>
-      </c>
-      <c r="P377" t="s">
-        <v>1662</v>
-      </c>
-      <c r="Q377" t="s">
-        <v>1676</v>
-      </c>
-      <c r="R377" t="s">
-        <v>1677</v>
-      </c>
-      <c r="S377" t="s">
-        <v>628</v>
-      </c>
-      <c r="T377" t="s">
-        <v>1678</v>
-      </c>
-      <c r="U377">
-        <v>1</v>
-      </c>
-      <c r="V377">
-        <v>17</v>
-      </c>
-      <c r="W377">
-        <v>9</v>
-      </c>
-      <c r="X377">
-        <v>7</v>
-      </c>
-      <c r="Y377" t="s">
-        <v>620</v>
-      </c>
-      <c r="Z377">
-        <v>-180</v>
-      </c>
-      <c r="AA377" t="s">
-        <v>1621</v>
-      </c>
-      <c r="AB377" t="s">
-        <v>1622</v>
-      </c>
-      <c r="AC377" t="s">
-        <v>1092</v>
-      </c>
-      <c r="AD377" t="s">
-        <v>1249</v>
-      </c>
-      <c r="AE377">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="378" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="378" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A378">
         <v>117</v>
       </c>
@@ -33357,73 +31908,16 @@
         <v>116</v>
       </c>
       <c r="C378" t="s">
+        <v>1611</v>
+      </c>
+      <c r="D378">
+        <v>10000</v>
+      </c>
+      <c r="L378" t="s">
         <v>1592</v>
       </c>
-      <c r="F378" t="s">
-        <v>1593</v>
-      </c>
-      <c r="L378" t="s">
-        <v>1593</v>
-      </c>
-      <c r="M378" t="s">
-        <v>1679</v>
-      </c>
-      <c r="N378" t="s">
-        <v>1660</v>
-      </c>
-      <c r="O378" t="s">
-        <v>1661</v>
-      </c>
-      <c r="P378" t="s">
-        <v>1662</v>
-      </c>
-      <c r="Q378" t="s">
-        <v>1680</v>
-      </c>
-      <c r="R378" t="s">
-        <v>1681</v>
-      </c>
-      <c r="S378" t="s">
-        <v>1682</v>
-      </c>
-      <c r="T378" t="s">
-        <v>1683</v>
-      </c>
-      <c r="U378">
-        <v>1</v>
-      </c>
-      <c r="V378">
-        <v>27</v>
-      </c>
-      <c r="W378">
-        <v>14</v>
-      </c>
-      <c r="X378">
-        <v>17</v>
-      </c>
-      <c r="Y378" t="s">
-        <v>1150</v>
-      </c>
-      <c r="Z378">
-        <v>-180</v>
-      </c>
-      <c r="AA378" t="s">
-        <v>1621</v>
-      </c>
-      <c r="AB378" t="s">
-        <v>1622</v>
-      </c>
-      <c r="AC378" t="s">
-        <v>1249</v>
-      </c>
-      <c r="AD378" t="s">
-        <v>885</v>
-      </c>
-      <c r="AE378">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="379" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="379" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A379">
         <v>117</v>
       </c>
@@ -33431,73 +31925,16 @@
         <v>116</v>
       </c>
       <c r="C379" t="s">
+        <v>1612</v>
+      </c>
+      <c r="D379">
+        <v>10000</v>
+      </c>
+      <c r="L379" t="s">
         <v>1592</v>
       </c>
-      <c r="F379" t="s">
-        <v>1593</v>
-      </c>
-      <c r="L379" t="s">
-        <v>1593</v>
-      </c>
-      <c r="M379" t="s">
-        <v>1684</v>
-      </c>
-      <c r="N379" t="s">
-        <v>1615</v>
-      </c>
-      <c r="O379" t="s">
-        <v>1616</v>
-      </c>
-      <c r="P379" t="s">
-        <v>1617</v>
-      </c>
-      <c r="Q379" t="s">
-        <v>1685</v>
-      </c>
-      <c r="R379" t="s">
-        <v>1686</v>
-      </c>
-      <c r="S379" t="s">
-        <v>1041</v>
-      </c>
-      <c r="T379" t="s">
-        <v>1687</v>
-      </c>
-      <c r="U379">
-        <v>1</v>
-      </c>
-      <c r="V379">
-        <v>27</v>
-      </c>
-      <c r="W379">
-        <v>14</v>
-      </c>
-      <c r="X379">
-        <v>17</v>
-      </c>
-      <c r="Y379" t="s">
-        <v>1478</v>
-      </c>
-      <c r="Z379">
-        <v>-180</v>
-      </c>
-      <c r="AA379" t="s">
-        <v>1621</v>
-      </c>
-      <c r="AB379" t="s">
-        <v>1622</v>
-      </c>
-      <c r="AC379" t="s">
-        <v>1249</v>
-      </c>
-      <c r="AD379" t="s">
-        <v>885</v>
-      </c>
-      <c r="AE379">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="380" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="380" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A380">
         <v>122</v>
       </c>
@@ -33505,73 +31942,16 @@
         <v>120</v>
       </c>
       <c r="C380" t="s">
+        <v>1613</v>
+      </c>
+      <c r="D380">
+        <v>10000</v>
+      </c>
+      <c r="L380" t="s">
         <v>1592</v>
       </c>
-      <c r="F380" t="s">
-        <v>1593</v>
-      </c>
-      <c r="L380" t="s">
-        <v>1593</v>
-      </c>
-      <c r="M380" t="s">
-        <v>1688</v>
-      </c>
-      <c r="N380" t="s">
-        <v>1615</v>
-      </c>
-      <c r="O380" t="s">
-        <v>1616</v>
-      </c>
-      <c r="P380" t="s">
-        <v>1617</v>
-      </c>
-      <c r="Q380" t="s">
-        <v>1689</v>
-      </c>
-      <c r="R380" t="s">
-        <v>1690</v>
-      </c>
-      <c r="S380" t="s">
-        <v>827</v>
-      </c>
-      <c r="T380" t="s">
-        <v>1691</v>
-      </c>
-      <c r="U380">
-        <v>1</v>
-      </c>
-      <c r="V380">
-        <v>27</v>
-      </c>
-      <c r="W380">
-        <v>14</v>
-      </c>
-      <c r="X380">
-        <v>17</v>
-      </c>
-      <c r="Y380" t="s">
-        <v>1692</v>
-      </c>
-      <c r="Z380">
-        <v>-180</v>
-      </c>
-      <c r="AA380" t="s">
-        <v>1621</v>
-      </c>
-      <c r="AB380" t="s">
-        <v>1622</v>
-      </c>
-      <c r="AC380" t="s">
-        <v>1249</v>
-      </c>
-      <c r="AD380" t="s">
-        <v>885</v>
-      </c>
-      <c r="AE380">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="381" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="381" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A381">
         <v>122</v>
       </c>
@@ -33579,73 +31959,16 @@
         <v>121</v>
       </c>
       <c r="C381" t="s">
+        <v>1614</v>
+      </c>
+      <c r="D381">
+        <v>10000</v>
+      </c>
+      <c r="L381" t="s">
         <v>1592</v>
       </c>
-      <c r="F381" t="s">
-        <v>1593</v>
-      </c>
-      <c r="L381" t="s">
-        <v>1593</v>
-      </c>
-      <c r="M381" t="s">
-        <v>1693</v>
-      </c>
-      <c r="N381" t="s">
-        <v>1667</v>
-      </c>
-      <c r="O381" t="s">
-        <v>1629</v>
-      </c>
-      <c r="P381" t="s">
-        <v>1617</v>
-      </c>
-      <c r="Q381" t="s">
-        <v>1668</v>
-      </c>
-      <c r="R381" t="s">
-        <v>1617</v>
-      </c>
-      <c r="S381" t="s">
-        <v>615</v>
-      </c>
-      <c r="T381" t="s">
-        <v>1669</v>
-      </c>
-      <c r="U381">
-        <v>1</v>
-      </c>
-      <c r="V381">
-        <v>21</v>
-      </c>
-      <c r="W381">
-        <v>11</v>
-      </c>
-      <c r="X381">
-        <v>11</v>
-      </c>
-      <c r="Y381" t="s">
-        <v>620</v>
-      </c>
-      <c r="Z381">
-        <v>0</v>
-      </c>
-      <c r="AA381" t="s">
-        <v>1621</v>
-      </c>
-      <c r="AB381" t="s">
-        <v>1622</v>
-      </c>
-      <c r="AC381" t="s">
-        <v>619</v>
-      </c>
-      <c r="AD381" t="s">
-        <v>972</v>
-      </c>
-      <c r="AE381">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="382" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="382" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A382">
         <v>132</v>
       </c>
@@ -33653,61 +31976,16 @@
         <v>131</v>
       </c>
       <c r="C382" t="s">
+        <v>1615</v>
+      </c>
+      <c r="D382">
+        <v>10000</v>
+      </c>
+      <c r="L382" t="s">
         <v>1592</v>
       </c>
-      <c r="F382" t="s">
-        <v>1593</v>
-      </c>
-      <c r="L382" t="s">
-        <v>1593</v>
-      </c>
-      <c r="M382" t="s">
-        <v>1694</v>
-      </c>
-      <c r="N382" t="s">
-        <v>1695</v>
-      </c>
-      <c r="O382" t="s">
-        <v>1696</v>
-      </c>
-      <c r="P382" t="s">
-        <v>1697</v>
-      </c>
-      <c r="Q382" t="s">
-        <v>1698</v>
-      </c>
-      <c r="R382" t="s">
-        <v>1699</v>
-      </c>
-      <c r="S382" t="s">
-        <v>1115</v>
-      </c>
-      <c r="T382" t="s">
-        <v>1697</v>
-      </c>
-      <c r="U382">
-        <v>-2</v>
-      </c>
-      <c r="V382">
-        <v>2</v>
-      </c>
-      <c r="W382">
-        <v>0</v>
-      </c>
-      <c r="X382">
-        <v>0</v>
-      </c>
-      <c r="Y382" t="s">
-        <v>994</v>
-      </c>
-      <c r="Z382">
-        <v>0</v>
-      </c>
-      <c r="AA382" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="383" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="383" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A383">
         <v>145</v>
       </c>
@@ -33715,61 +31993,16 @@
         <v>141</v>
       </c>
       <c r="C383" t="s">
+        <v>1616</v>
+      </c>
+      <c r="D383">
+        <v>10000</v>
+      </c>
+      <c r="L383" t="s">
         <v>1592</v>
       </c>
-      <c r="F383" t="s">
-        <v>1593</v>
-      </c>
-      <c r="L383" t="s">
-        <v>1593</v>
-      </c>
-      <c r="M383" t="s">
-        <v>1700</v>
-      </c>
-      <c r="N383" t="s">
-        <v>1701</v>
-      </c>
-      <c r="O383" t="s">
-        <v>1702</v>
-      </c>
-      <c r="P383" t="s">
-        <v>1703</v>
-      </c>
-      <c r="Q383" t="s">
-        <v>1704</v>
-      </c>
-      <c r="R383" t="s">
-        <v>1705</v>
-      </c>
-      <c r="S383" t="s">
-        <v>913</v>
-      </c>
-      <c r="T383" t="s">
-        <v>1706</v>
-      </c>
-      <c r="U383">
-        <v>1</v>
-      </c>
-      <c r="V383">
-        <v>1</v>
-      </c>
-      <c r="W383">
-        <v>1</v>
-      </c>
-      <c r="X383">
-        <v>1</v>
-      </c>
-      <c r="Y383" t="s">
-        <v>619</v>
-      </c>
-      <c r="Z383">
-        <v>0</v>
-      </c>
-      <c r="AA383" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="384" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="384" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A384">
         <v>145</v>
       </c>
@@ -33777,61 +32010,16 @@
         <v>143</v>
       </c>
       <c r="C384" t="s">
+        <v>1617</v>
+      </c>
+      <c r="D384">
+        <v>10000</v>
+      </c>
+      <c r="L384" t="s">
         <v>1592</v>
       </c>
-      <c r="F384" t="s">
-        <v>1593</v>
-      </c>
-      <c r="L384" t="s">
-        <v>1593</v>
-      </c>
-      <c r="M384" t="s">
-        <v>1707</v>
-      </c>
-      <c r="N384" t="s">
-        <v>1701</v>
-      </c>
-      <c r="O384" t="s">
-        <v>1702</v>
-      </c>
-      <c r="P384" t="s">
-        <v>1708</v>
-      </c>
-      <c r="Q384" t="s">
-        <v>1641</v>
-      </c>
-      <c r="R384" t="s">
-        <v>1652</v>
-      </c>
-      <c r="S384" t="s">
-        <v>913</v>
-      </c>
-      <c r="T384" t="s">
-        <v>1706</v>
-      </c>
-      <c r="U384">
-        <v>1</v>
-      </c>
-      <c r="V384">
-        <v>1</v>
-      </c>
-      <c r="W384">
-        <v>1</v>
-      </c>
-      <c r="X384">
-        <v>1</v>
-      </c>
-      <c r="Y384" t="s">
-        <v>619</v>
-      </c>
-      <c r="Z384">
-        <v>0</v>
-      </c>
-      <c r="AA384" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="385" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="385" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A385">
         <v>147</v>
       </c>
@@ -33839,73 +32027,16 @@
         <v>146</v>
       </c>
       <c r="C385" t="s">
+        <v>1618</v>
+      </c>
+      <c r="D385">
+        <v>10000</v>
+      </c>
+      <c r="L385" t="s">
         <v>1592</v>
       </c>
-      <c r="F385" t="s">
-        <v>1593</v>
-      </c>
-      <c r="L385" t="s">
-        <v>1593</v>
-      </c>
-      <c r="M385" t="s">
-        <v>1709</v>
-      </c>
-      <c r="N385" t="s">
-        <v>1616</v>
-      </c>
-      <c r="O385" t="s">
-        <v>1616</v>
-      </c>
-      <c r="P385" t="s">
-        <v>1710</v>
-      </c>
-      <c r="Q385" t="s">
-        <v>1711</v>
-      </c>
-      <c r="R385" t="s">
-        <v>1643</v>
-      </c>
-      <c r="S385" t="s">
-        <v>1041</v>
-      </c>
-      <c r="T385" t="s">
-        <v>1712</v>
-      </c>
-      <c r="U385">
-        <v>-8</v>
-      </c>
-      <c r="V385">
-        <v>8</v>
-      </c>
-      <c r="W385">
-        <v>0</v>
-      </c>
-      <c r="X385">
-        <v>0</v>
-      </c>
-      <c r="Y385" t="s">
-        <v>619</v>
-      </c>
-      <c r="Z385">
-        <v>1</v>
-      </c>
-      <c r="AA385" t="s">
-        <v>1621</v>
-      </c>
-      <c r="AB385" t="s">
-        <v>1622</v>
-      </c>
-      <c r="AC385" t="s">
-        <v>1654</v>
-      </c>
-      <c r="AD385" t="s">
-        <v>972</v>
-      </c>
-      <c r="AE385">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="386" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="386" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A386">
         <v>161</v>
       </c>
@@ -33913,61 +32044,16 @@
         <v>160</v>
       </c>
       <c r="C386" t="s">
+        <v>1619</v>
+      </c>
+      <c r="D386">
+        <v>10000</v>
+      </c>
+      <c r="L386" t="s">
         <v>1592</v>
       </c>
-      <c r="F386" t="s">
-        <v>1593</v>
-      </c>
-      <c r="L386" t="s">
-        <v>1593</v>
-      </c>
-      <c r="M386" t="s">
-        <v>1713</v>
-      </c>
-      <c r="N386" t="s">
-        <v>1616</v>
-      </c>
-      <c r="O386" t="s">
-        <v>1714</v>
-      </c>
-      <c r="P386" t="s">
-        <v>1715</v>
-      </c>
-      <c r="Q386" t="s">
-        <v>1716</v>
-      </c>
-      <c r="R386" t="s">
-        <v>1717</v>
-      </c>
-      <c r="S386" t="s">
-        <v>993</v>
-      </c>
-      <c r="T386" t="s">
-        <v>1718</v>
-      </c>
-      <c r="U386">
-        <v>1</v>
-      </c>
-      <c r="V386">
-        <v>1</v>
-      </c>
-      <c r="W386">
-        <v>1</v>
-      </c>
-      <c r="X386">
-        <v>1</v>
-      </c>
-      <c r="Y386" t="s">
-        <v>619</v>
-      </c>
-      <c r="Z386">
-        <v>0</v>
-      </c>
-      <c r="AA386" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="387" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="387" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A387">
         <v>176</v>
       </c>
@@ -33975,61 +32061,16 @@
         <v>175</v>
       </c>
       <c r="C387" t="s">
+        <v>1620</v>
+      </c>
+      <c r="D387">
+        <v>10000</v>
+      </c>
+      <c r="L387" t="s">
         <v>1592</v>
       </c>
-      <c r="F387" t="s">
-        <v>1593</v>
-      </c>
-      <c r="L387" t="s">
-        <v>1593</v>
-      </c>
-      <c r="M387" t="s">
-        <v>1719</v>
-      </c>
-      <c r="N387" t="s">
-        <v>1720</v>
-      </c>
-      <c r="O387" t="s">
-        <v>1702</v>
-      </c>
-      <c r="P387" t="s">
-        <v>1721</v>
-      </c>
-      <c r="Q387" t="s">
-        <v>1722</v>
-      </c>
-      <c r="R387" t="s">
-        <v>1723</v>
-      </c>
-      <c r="S387" t="s">
-        <v>629</v>
-      </c>
-      <c r="T387" t="s">
-        <v>1724</v>
-      </c>
-      <c r="U387">
-        <v>1</v>
-      </c>
-      <c r="V387">
-        <v>1</v>
-      </c>
-      <c r="W387">
-        <v>1</v>
-      </c>
-      <c r="X387">
-        <v>1</v>
-      </c>
-      <c r="Y387" t="s">
-        <v>619</v>
-      </c>
-      <c r="Z387">
-        <v>0</v>
-      </c>
-      <c r="AA387" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="388" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="388" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A388">
         <v>190</v>
       </c>
@@ -34037,73 +32078,16 @@
         <v>189</v>
       </c>
       <c r="C388" t="s">
+        <v>1621</v>
+      </c>
+      <c r="D388">
+        <v>10000</v>
+      </c>
+      <c r="L388" t="s">
         <v>1592</v>
       </c>
-      <c r="F388" t="s">
-        <v>1593</v>
-      </c>
-      <c r="L388" t="s">
-        <v>1593</v>
-      </c>
-      <c r="M388" t="s">
-        <v>1725</v>
-      </c>
-      <c r="N388" t="s">
-        <v>1615</v>
-      </c>
-      <c r="O388" t="s">
-        <v>1616</v>
-      </c>
-      <c r="P388" t="s">
-        <v>1615</v>
-      </c>
-      <c r="Q388" t="s">
-        <v>1656</v>
-      </c>
-      <c r="R388" t="s">
-        <v>1657</v>
-      </c>
-      <c r="S388" t="s">
-        <v>628</v>
-      </c>
-      <c r="T388" t="s">
-        <v>1658</v>
-      </c>
-      <c r="U388">
-        <v>1</v>
-      </c>
-      <c r="V388">
-        <v>17</v>
-      </c>
-      <c r="W388">
-        <v>9</v>
-      </c>
-      <c r="X388">
-        <v>14</v>
-      </c>
-      <c r="Y388" t="s">
-        <v>620</v>
-      </c>
-      <c r="Z388">
-        <v>-180</v>
-      </c>
-      <c r="AA388" t="s">
-        <v>1621</v>
-      </c>
-      <c r="AB388" t="s">
-        <v>1622</v>
-      </c>
-      <c r="AC388" t="s">
-        <v>1249</v>
-      </c>
-      <c r="AD388" t="s">
-        <v>885</v>
-      </c>
-      <c r="AE388">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="389" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="389" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A389">
         <v>192</v>
       </c>
@@ -34111,61 +32095,16 @@
         <v>193</v>
       </c>
       <c r="C389" t="s">
+        <v>1622</v>
+      </c>
+      <c r="D389">
+        <v>10000</v>
+      </c>
+      <c r="L389" t="s">
         <v>1592</v>
       </c>
-      <c r="F389" t="s">
-        <v>1593</v>
-      </c>
-      <c r="L389" t="s">
-        <v>1593</v>
-      </c>
-      <c r="M389" t="s">
-        <v>1726</v>
-      </c>
-      <c r="N389" t="s">
-        <v>1727</v>
-      </c>
-      <c r="O389" t="s">
-        <v>1727</v>
-      </c>
-      <c r="P389" t="s">
-        <v>1662</v>
-      </c>
-      <c r="Q389" t="s">
-        <v>1067</v>
-      </c>
-      <c r="R389" t="s">
-        <v>1728</v>
-      </c>
-      <c r="S389" t="s">
-        <v>1041</v>
-      </c>
-      <c r="T389" t="s">
-        <v>1729</v>
-      </c>
-      <c r="U389">
-        <v>-10</v>
-      </c>
-      <c r="V389">
-        <v>10</v>
-      </c>
-      <c r="W389">
-        <v>0</v>
-      </c>
-      <c r="X389">
-        <v>0</v>
-      </c>
-      <c r="Y389" t="s">
-        <v>619</v>
-      </c>
-      <c r="Z389">
-        <v>1</v>
-      </c>
-      <c r="AA389" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="390" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="390" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A390">
         <v>198</v>
       </c>
@@ -34173,73 +32112,16 @@
         <v>197</v>
       </c>
       <c r="C390" t="s">
+        <v>1623</v>
+      </c>
+      <c r="D390">
+        <v>10000</v>
+      </c>
+      <c r="L390" t="s">
         <v>1592</v>
       </c>
-      <c r="F390" t="s">
-        <v>1593</v>
-      </c>
-      <c r="L390" t="s">
-        <v>1593</v>
-      </c>
-      <c r="M390" t="s">
-        <v>1730</v>
-      </c>
-      <c r="N390" t="s">
-        <v>1667</v>
-      </c>
-      <c r="O390" t="s">
-        <v>1731</v>
-      </c>
-      <c r="P390" t="s">
-        <v>1732</v>
-      </c>
-      <c r="Q390" t="s">
-        <v>1733</v>
-      </c>
-      <c r="R390" t="s">
-        <v>1660</v>
-      </c>
-      <c r="S390" t="s">
-        <v>699</v>
-      </c>
-      <c r="T390" t="s">
-        <v>1734</v>
-      </c>
-      <c r="U390">
-        <v>1</v>
-      </c>
-      <c r="V390">
-        <v>21</v>
-      </c>
-      <c r="W390">
-        <v>11</v>
-      </c>
-      <c r="X390">
-        <v>9</v>
-      </c>
-      <c r="Y390" t="s">
-        <v>768</v>
-      </c>
-      <c r="Z390">
-        <v>0</v>
-      </c>
-      <c r="AA390" t="s">
-        <v>1621</v>
-      </c>
-      <c r="AB390" t="s">
-        <v>1622</v>
-      </c>
-      <c r="AC390" t="s">
-        <v>1016</v>
-      </c>
-      <c r="AD390" t="s">
-        <v>1249</v>
-      </c>
-      <c r="AE390">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="391" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="391" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A391">
         <v>214</v>
       </c>
@@ -34247,73 +32129,16 @@
         <v>210</v>
       </c>
       <c r="C391" t="s">
+        <v>1624</v>
+      </c>
+      <c r="D391">
+        <v>10000</v>
+      </c>
+      <c r="L391" t="s">
         <v>1592</v>
       </c>
-      <c r="F391" t="s">
-        <v>1593</v>
-      </c>
-      <c r="L391" t="s">
-        <v>1593</v>
-      </c>
-      <c r="M391" t="s">
-        <v>1735</v>
-      </c>
-      <c r="N391" t="s">
-        <v>1667</v>
-      </c>
-      <c r="O391" t="s">
-        <v>1736</v>
-      </c>
-      <c r="P391" t="s">
-        <v>1615</v>
-      </c>
-      <c r="Q391" t="s">
-        <v>1737</v>
-      </c>
-      <c r="R391" t="s">
-        <v>1738</v>
-      </c>
-      <c r="S391" t="s">
-        <v>628</v>
-      </c>
-      <c r="T391" t="s">
-        <v>1739</v>
-      </c>
-      <c r="U391">
-        <v>1</v>
-      </c>
-      <c r="V391">
-        <v>21</v>
-      </c>
-      <c r="W391">
-        <v>11</v>
-      </c>
-      <c r="X391">
-        <v>9</v>
-      </c>
-      <c r="Y391" t="s">
-        <v>768</v>
-      </c>
-      <c r="Z391">
-        <v>0</v>
-      </c>
-      <c r="AA391" t="s">
-        <v>1621</v>
-      </c>
-      <c r="AB391" t="s">
-        <v>1622</v>
-      </c>
-      <c r="AC391" t="s">
-        <v>1092</v>
-      </c>
-      <c r="AD391" t="s">
-        <v>1478</v>
-      </c>
-      <c r="AE391">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="392" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="392" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A392">
         <v>214</v>
       </c>
@@ -34321,73 +32146,16 @@
         <v>211</v>
       </c>
       <c r="C392" t="s">
+        <v>1625</v>
+      </c>
+      <c r="D392">
+        <v>10000</v>
+      </c>
+      <c r="L392" t="s">
         <v>1592</v>
       </c>
-      <c r="F392" t="s">
-        <v>1593</v>
-      </c>
-      <c r="L392" t="s">
-        <v>1593</v>
-      </c>
-      <c r="M392" t="s">
-        <v>1740</v>
-      </c>
-      <c r="N392" t="s">
-        <v>1667</v>
-      </c>
-      <c r="O392" t="s">
-        <v>1741</v>
-      </c>
-      <c r="P392" t="s">
-        <v>1605</v>
-      </c>
-      <c r="Q392" t="s">
-        <v>1668</v>
-      </c>
-      <c r="R392" t="s">
-        <v>1742</v>
-      </c>
-      <c r="S392" t="s">
-        <v>628</v>
-      </c>
-      <c r="T392" t="s">
-        <v>1743</v>
-      </c>
-      <c r="U392">
-        <v>1</v>
-      </c>
-      <c r="V392">
-        <v>21</v>
-      </c>
-      <c r="W392">
-        <v>11</v>
-      </c>
-      <c r="X392">
-        <v>9</v>
-      </c>
-      <c r="Y392" t="s">
-        <v>1249</v>
-      </c>
-      <c r="Z392">
-        <v>0</v>
-      </c>
-      <c r="AA392" t="s">
-        <v>1621</v>
-      </c>
-      <c r="AB392" t="s">
-        <v>1622</v>
-      </c>
-      <c r="AC392" t="s">
-        <v>885</v>
-      </c>
-      <c r="AD392" t="s">
-        <v>1016</v>
-      </c>
-      <c r="AE392">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="393" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="393" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A393">
         <v>217</v>
       </c>
@@ -34395,73 +32163,16 @@
         <v>216</v>
       </c>
       <c r="C393" t="s">
+        <v>1626</v>
+      </c>
+      <c r="D393">
+        <v>10000</v>
+      </c>
+      <c r="L393" t="s">
         <v>1592</v>
       </c>
-      <c r="F393" t="s">
-        <v>1593</v>
-      </c>
-      <c r="L393" t="s">
-        <v>1593</v>
-      </c>
-      <c r="M393" t="s">
-        <v>1744</v>
-      </c>
-      <c r="N393" t="s">
-        <v>1667</v>
-      </c>
-      <c r="O393" t="s">
-        <v>1736</v>
-      </c>
-      <c r="P393" t="s">
-        <v>1615</v>
-      </c>
-      <c r="Q393" t="s">
-        <v>1745</v>
-      </c>
-      <c r="R393" t="s">
-        <v>1746</v>
-      </c>
-      <c r="S393" t="s">
-        <v>628</v>
-      </c>
-      <c r="T393" t="s">
-        <v>1747</v>
-      </c>
-      <c r="U393">
-        <v>1</v>
-      </c>
-      <c r="V393">
-        <v>21</v>
-      </c>
-      <c r="W393">
-        <v>11</v>
-      </c>
-      <c r="X393">
-        <v>9</v>
-      </c>
-      <c r="Y393" t="s">
-        <v>768</v>
-      </c>
-      <c r="Z393">
-        <v>0</v>
-      </c>
-      <c r="AA393" t="s">
-        <v>1621</v>
-      </c>
-      <c r="AB393" t="s">
-        <v>1622</v>
-      </c>
-      <c r="AC393" t="s">
-        <v>1016</v>
-      </c>
-      <c r="AD393" t="s">
-        <v>1249</v>
-      </c>
-      <c r="AE393">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="394" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="394" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A394">
         <v>221</v>
       </c>
@@ -34469,73 +32180,16 @@
         <v>220</v>
       </c>
       <c r="C394" t="s">
+        <v>1627</v>
+      </c>
+      <c r="D394">
+        <v>10000</v>
+      </c>
+      <c r="L394" t="s">
         <v>1592</v>
       </c>
-      <c r="F394" t="s">
-        <v>1593</v>
-      </c>
-      <c r="L394" t="s">
-        <v>1593</v>
-      </c>
-      <c r="M394" t="s">
-        <v>1748</v>
-      </c>
-      <c r="N394" t="s">
-        <v>1667</v>
-      </c>
-      <c r="O394" t="s">
-        <v>1736</v>
-      </c>
-      <c r="P394" t="s">
-        <v>1615</v>
-      </c>
-      <c r="Q394" t="s">
-        <v>1749</v>
-      </c>
-      <c r="R394" t="s">
-        <v>1746</v>
-      </c>
-      <c r="S394" t="s">
-        <v>628</v>
-      </c>
-      <c r="T394" t="s">
-        <v>1750</v>
-      </c>
-      <c r="U394">
-        <v>1</v>
-      </c>
-      <c r="V394">
-        <v>21</v>
-      </c>
-      <c r="W394">
-        <v>11</v>
-      </c>
-      <c r="X394">
-        <v>9</v>
-      </c>
-      <c r="Y394" t="s">
-        <v>768</v>
-      </c>
-      <c r="Z394">
-        <v>0</v>
-      </c>
-      <c r="AA394" t="s">
-        <v>1621</v>
-      </c>
-      <c r="AB394" t="s">
-        <v>1622</v>
-      </c>
-      <c r="AC394" t="s">
-        <v>1016</v>
-      </c>
-      <c r="AD394" t="s">
-        <v>1249</v>
-      </c>
-      <c r="AE394">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="395" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="395" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A395">
         <v>221</v>
       </c>
@@ -34543,73 +32197,16 @@
         <v>220</v>
       </c>
       <c r="C395" t="s">
+        <v>1628</v>
+      </c>
+      <c r="D395">
+        <v>10000</v>
+      </c>
+      <c r="L395" t="s">
         <v>1592</v>
       </c>
-      <c r="F395" t="s">
-        <v>1593</v>
-      </c>
-      <c r="L395" t="s">
-        <v>1593</v>
-      </c>
-      <c r="M395" t="s">
-        <v>1751</v>
-      </c>
-      <c r="N395" t="s">
-        <v>1667</v>
-      </c>
-      <c r="O395" t="s">
-        <v>1736</v>
-      </c>
-      <c r="P395" t="s">
-        <v>1615</v>
-      </c>
-      <c r="Q395" t="s">
-        <v>1749</v>
-      </c>
-      <c r="R395" t="s">
-        <v>1746</v>
-      </c>
-      <c r="S395" t="s">
-        <v>628</v>
-      </c>
-      <c r="T395" t="s">
-        <v>1750</v>
-      </c>
-      <c r="U395">
-        <v>1</v>
-      </c>
-      <c r="V395">
-        <v>21</v>
-      </c>
-      <c r="W395">
-        <v>11</v>
-      </c>
-      <c r="X395">
-        <v>9</v>
-      </c>
-      <c r="Y395" t="s">
-        <v>768</v>
-      </c>
-      <c r="Z395">
-        <v>0</v>
-      </c>
-      <c r="AA395" t="s">
-        <v>1621</v>
-      </c>
-      <c r="AB395" t="s">
-        <v>1622</v>
-      </c>
-      <c r="AC395" t="s">
-        <v>1016</v>
-      </c>
-      <c r="AD395" t="s">
-        <v>1249</v>
-      </c>
-      <c r="AE395">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="396" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="396" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A396">
         <v>231</v>
       </c>
@@ -34617,61 +32214,16 @@
         <v>229</v>
       </c>
       <c r="C396" t="s">
+        <v>1629</v>
+      </c>
+      <c r="D396">
+        <v>10000</v>
+      </c>
+      <c r="L396" t="s">
         <v>1592</v>
       </c>
-      <c r="F396" t="s">
-        <v>1593</v>
-      </c>
-      <c r="L396" t="s">
-        <v>1593</v>
-      </c>
-      <c r="M396" t="s">
-        <v>1752</v>
-      </c>
-      <c r="N396" t="s">
-        <v>1727</v>
-      </c>
-      <c r="O396" t="s">
-        <v>1753</v>
-      </c>
-      <c r="P396" t="s">
-        <v>1754</v>
-      </c>
-      <c r="Q396" t="s">
-        <v>1059</v>
-      </c>
-      <c r="R396" t="s">
-        <v>1755</v>
-      </c>
-      <c r="S396" t="s">
-        <v>823</v>
-      </c>
-      <c r="T396" t="s">
-        <v>1756</v>
-      </c>
-      <c r="U396">
-        <v>1</v>
-      </c>
-      <c r="V396">
-        <v>1</v>
-      </c>
-      <c r="W396">
-        <v>1</v>
-      </c>
-      <c r="X396">
-        <v>1</v>
-      </c>
-      <c r="Y396" t="s">
-        <v>619</v>
-      </c>
-      <c r="Z396">
-        <v>0</v>
-      </c>
-      <c r="AA396" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="397" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="397" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A397">
         <v>232</v>
       </c>
@@ -34679,61 +32231,16 @@
         <v>230</v>
       </c>
       <c r="C397" t="s">
+        <v>1630</v>
+      </c>
+      <c r="D397">
+        <v>10000</v>
+      </c>
+      <c r="L397" t="s">
         <v>1592</v>
       </c>
-      <c r="F397" t="s">
-        <v>1593</v>
-      </c>
-      <c r="L397" t="s">
-        <v>1593</v>
-      </c>
-      <c r="M397" t="s">
-        <v>1757</v>
-      </c>
-      <c r="N397" t="s">
-        <v>1758</v>
-      </c>
-      <c r="O397" t="s">
-        <v>1625</v>
-      </c>
-      <c r="P397" t="s">
-        <v>1759</v>
-      </c>
-      <c r="Q397" t="s">
-        <v>1760</v>
-      </c>
-      <c r="R397" t="s">
-        <v>1761</v>
-      </c>
-      <c r="S397" t="s">
-        <v>619</v>
-      </c>
-      <c r="T397" t="s">
-        <v>1632</v>
-      </c>
-      <c r="U397">
-        <v>1</v>
-      </c>
-      <c r="V397">
-        <v>1</v>
-      </c>
-      <c r="W397">
-        <v>1</v>
-      </c>
-      <c r="X397">
-        <v>1</v>
-      </c>
-      <c r="Y397" t="s">
-        <v>619</v>
-      </c>
-      <c r="Z397">
-        <v>0</v>
-      </c>
-      <c r="AA397" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="398" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="398" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A398">
         <v>294</v>
       </c>
@@ -34741,61 +32248,16 @@
         <v>237</v>
       </c>
       <c r="C398" t="s">
+        <v>1631</v>
+      </c>
+      <c r="D398">
+        <v>10000</v>
+      </c>
+      <c r="L398" t="s">
         <v>1592</v>
       </c>
-      <c r="F398" t="s">
-        <v>1593</v>
-      </c>
-      <c r="L398" t="s">
-        <v>1593</v>
-      </c>
-      <c r="M398" t="s">
-        <v>1762</v>
-      </c>
-      <c r="N398" t="s">
-        <v>1727</v>
-      </c>
-      <c r="O398" t="s">
-        <v>1763</v>
-      </c>
-      <c r="P398" t="s">
-        <v>1764</v>
-      </c>
-      <c r="Q398" t="s">
-        <v>1765</v>
-      </c>
-      <c r="R398" t="s">
-        <v>1766</v>
-      </c>
-      <c r="S398" t="s">
-        <v>1767</v>
-      </c>
-      <c r="T398" t="s">
-        <v>1768</v>
-      </c>
-      <c r="U398">
-        <v>1</v>
-      </c>
-      <c r="V398">
-        <v>1</v>
-      </c>
-      <c r="W398">
-        <v>1</v>
-      </c>
-      <c r="X398">
-        <v>1</v>
-      </c>
-      <c r="Y398" t="s">
-        <v>619</v>
-      </c>
-      <c r="Z398">
-        <v>0</v>
-      </c>
-      <c r="AA398" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="399" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="399" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A399">
         <v>248</v>
       </c>
@@ -34803,73 +32265,16 @@
         <v>247</v>
       </c>
       <c r="C399" t="s">
+        <v>1632</v>
+      </c>
+      <c r="D399">
+        <v>10000</v>
+      </c>
+      <c r="L399" t="s">
         <v>1592</v>
       </c>
-      <c r="F399" t="s">
-        <v>1593</v>
-      </c>
-      <c r="L399" t="s">
-        <v>1593</v>
-      </c>
-      <c r="M399" t="s">
-        <v>1769</v>
-      </c>
-      <c r="N399" t="s">
-        <v>1667</v>
-      </c>
-      <c r="O399" t="s">
-        <v>1736</v>
-      </c>
-      <c r="P399" t="s">
-        <v>1615</v>
-      </c>
-      <c r="Q399" t="s">
-        <v>1770</v>
-      </c>
-      <c r="R399" t="s">
-        <v>1771</v>
-      </c>
-      <c r="S399" t="s">
-        <v>628</v>
-      </c>
-      <c r="T399" t="s">
-        <v>1739</v>
-      </c>
-      <c r="U399">
-        <v>1</v>
-      </c>
-      <c r="V399">
-        <v>21</v>
-      </c>
-      <c r="W399">
-        <v>11</v>
-      </c>
-      <c r="X399">
-        <v>9</v>
-      </c>
-      <c r="Y399" t="s">
-        <v>768</v>
-      </c>
-      <c r="Z399">
-        <v>0</v>
-      </c>
-      <c r="AA399" t="s">
-        <v>1621</v>
-      </c>
-      <c r="AB399" t="s">
-        <v>1622</v>
-      </c>
-      <c r="AC399" t="s">
-        <v>1016</v>
-      </c>
-      <c r="AD399" t="s">
-        <v>1249</v>
-      </c>
-      <c r="AE399">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="400" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="400" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A400">
         <v>253</v>
       </c>
@@ -34877,73 +32282,16 @@
         <v>252</v>
       </c>
       <c r="C400" t="s">
+        <v>1633</v>
+      </c>
+      <c r="D400">
+        <v>10000</v>
+      </c>
+      <c r="L400" t="s">
         <v>1592</v>
       </c>
-      <c r="F400" t="s">
-        <v>1593</v>
-      </c>
-      <c r="L400" t="s">
-        <v>1593</v>
-      </c>
-      <c r="M400" t="s">
-        <v>1772</v>
-      </c>
-      <c r="N400" t="s">
-        <v>1667</v>
-      </c>
-      <c r="O400" t="s">
-        <v>1736</v>
-      </c>
-      <c r="P400" t="s">
-        <v>1615</v>
-      </c>
-      <c r="Q400" t="s">
-        <v>1773</v>
-      </c>
-      <c r="R400" t="s">
-        <v>1746</v>
-      </c>
-      <c r="S400" t="s">
-        <v>628</v>
-      </c>
-      <c r="T400" t="s">
-        <v>1774</v>
-      </c>
-      <c r="U400">
-        <v>1</v>
-      </c>
-      <c r="V400">
-        <v>21</v>
-      </c>
-      <c r="W400">
-        <v>11</v>
-      </c>
-      <c r="X400">
-        <v>9</v>
-      </c>
-      <c r="Y400" t="s">
-        <v>768</v>
-      </c>
-      <c r="Z400">
-        <v>0</v>
-      </c>
-      <c r="AA400" t="s">
-        <v>1621</v>
-      </c>
-      <c r="AB400" t="s">
-        <v>1622</v>
-      </c>
-      <c r="AC400" t="s">
-        <v>1016</v>
-      </c>
-      <c r="AD400" t="s">
-        <v>1249</v>
-      </c>
-      <c r="AE400">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="401" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="401" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A401">
         <v>253</v>
       </c>
@@ -34951,73 +32299,16 @@
         <v>252</v>
       </c>
       <c r="C401" t="s">
+        <v>1634</v>
+      </c>
+      <c r="D401">
+        <v>10000</v>
+      </c>
+      <c r="L401" t="s">
         <v>1592</v>
       </c>
-      <c r="F401" t="s">
-        <v>1593</v>
-      </c>
-      <c r="L401" t="s">
-        <v>1593</v>
-      </c>
-      <c r="M401" t="s">
-        <v>1775</v>
-      </c>
-      <c r="N401" t="s">
-        <v>1667</v>
-      </c>
-      <c r="O401" t="s">
-        <v>1736</v>
-      </c>
-      <c r="P401" t="s">
-        <v>1615</v>
-      </c>
-      <c r="Q401" t="s">
-        <v>1770</v>
-      </c>
-      <c r="R401" t="s">
-        <v>1771</v>
-      </c>
-      <c r="S401" t="s">
-        <v>628</v>
-      </c>
-      <c r="T401" t="s">
-        <v>1739</v>
-      </c>
-      <c r="U401">
-        <v>1</v>
-      </c>
-      <c r="V401">
-        <v>21</v>
-      </c>
-      <c r="W401">
-        <v>11</v>
-      </c>
-      <c r="X401">
-        <v>9</v>
-      </c>
-      <c r="Y401" t="s">
-        <v>768</v>
-      </c>
-      <c r="Z401">
-        <v>0</v>
-      </c>
-      <c r="AA401" t="s">
-        <v>1621</v>
-      </c>
-      <c r="AB401" t="s">
-        <v>1622</v>
-      </c>
-      <c r="AC401" t="s">
-        <v>1016</v>
-      </c>
-      <c r="AD401" t="s">
-        <v>1249</v>
-      </c>
-      <c r="AE401">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="402" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="402" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A402">
         <v>256</v>
       </c>
@@ -35025,73 +32316,16 @@
         <v>255</v>
       </c>
       <c r="C402" t="s">
+        <v>1635</v>
+      </c>
+      <c r="D402">
+        <v>10000</v>
+      </c>
+      <c r="L402" t="s">
         <v>1592</v>
       </c>
-      <c r="F402" t="s">
-        <v>1593</v>
-      </c>
-      <c r="L402" t="s">
-        <v>1593</v>
-      </c>
-      <c r="M402" t="s">
-        <v>1776</v>
-      </c>
-      <c r="N402" t="s">
-        <v>1667</v>
-      </c>
-      <c r="O402" t="s">
-        <v>1731</v>
-      </c>
-      <c r="P402" t="s">
-        <v>1732</v>
-      </c>
-      <c r="Q402" t="s">
-        <v>1733</v>
-      </c>
-      <c r="R402" t="s">
-        <v>1660</v>
-      </c>
-      <c r="S402" t="s">
-        <v>699</v>
-      </c>
-      <c r="T402" t="s">
-        <v>1777</v>
-      </c>
-      <c r="U402">
-        <v>1</v>
-      </c>
-      <c r="V402">
-        <v>21</v>
-      </c>
-      <c r="W402">
-        <v>11</v>
-      </c>
-      <c r="X402">
-        <v>9</v>
-      </c>
-      <c r="Y402" t="s">
-        <v>768</v>
-      </c>
-      <c r="Z402">
-        <v>0</v>
-      </c>
-      <c r="AA402" t="s">
-        <v>1621</v>
-      </c>
-      <c r="AB402" t="s">
-        <v>1622</v>
-      </c>
-      <c r="AC402" t="s">
-        <v>1016</v>
-      </c>
-      <c r="AD402" t="s">
-        <v>1249</v>
-      </c>
-      <c r="AE402">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="403" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="403" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A403">
         <v>261</v>
       </c>
@@ -35099,73 +32333,16 @@
         <v>260</v>
       </c>
       <c r="C403" t="s">
+        <v>1636</v>
+      </c>
+      <c r="D403">
+        <v>10000</v>
+      </c>
+      <c r="L403" t="s">
         <v>1592</v>
       </c>
-      <c r="F403" t="s">
-        <v>1593</v>
-      </c>
-      <c r="L403" t="s">
-        <v>1593</v>
-      </c>
-      <c r="M403" t="s">
-        <v>1778</v>
-      </c>
-      <c r="N403" t="s">
-        <v>1667</v>
-      </c>
-      <c r="O403" t="s">
-        <v>1736</v>
-      </c>
-      <c r="P403" t="s">
-        <v>1615</v>
-      </c>
-      <c r="Q403" t="s">
-        <v>1749</v>
-      </c>
-      <c r="R403" t="s">
-        <v>1746</v>
-      </c>
-      <c r="S403" t="s">
-        <v>628</v>
-      </c>
-      <c r="T403" t="s">
-        <v>1779</v>
-      </c>
-      <c r="U403">
-        <v>1</v>
-      </c>
-      <c r="V403">
-        <v>21</v>
-      </c>
-      <c r="W403">
-        <v>11</v>
-      </c>
-      <c r="X403">
-        <v>9</v>
-      </c>
-      <c r="Y403" t="s">
-        <v>768</v>
-      </c>
-      <c r="Z403">
-        <v>0</v>
-      </c>
-      <c r="AA403" t="s">
-        <v>1621</v>
-      </c>
-      <c r="AB403" t="s">
-        <v>1622</v>
-      </c>
-      <c r="AC403" t="s">
-        <v>1016</v>
-      </c>
-      <c r="AD403" t="s">
-        <v>1249</v>
-      </c>
-      <c r="AE403">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="404" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="404" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A404">
         <v>268</v>
       </c>
@@ -35173,73 +32350,16 @@
         <v>267</v>
       </c>
       <c r="C404" t="s">
+        <v>1637</v>
+      </c>
+      <c r="D404">
+        <v>10000</v>
+      </c>
+      <c r="L404" t="s">
         <v>1592</v>
       </c>
-      <c r="F404" t="s">
-        <v>1593</v>
-      </c>
-      <c r="L404" t="s">
-        <v>1593</v>
-      </c>
-      <c r="M404" t="s">
-        <v>1780</v>
-      </c>
-      <c r="N404" t="s">
-        <v>1667</v>
-      </c>
-      <c r="O404" t="s">
-        <v>1736</v>
-      </c>
-      <c r="P404" t="s">
-        <v>1615</v>
-      </c>
-      <c r="Q404" t="s">
-        <v>1781</v>
-      </c>
-      <c r="R404" t="s">
-        <v>1771</v>
-      </c>
-      <c r="S404" t="s">
-        <v>628</v>
-      </c>
-      <c r="T404" t="s">
-        <v>1747</v>
-      </c>
-      <c r="U404">
-        <v>1</v>
-      </c>
-      <c r="V404">
-        <v>21</v>
-      </c>
-      <c r="W404">
-        <v>11</v>
-      </c>
-      <c r="X404">
-        <v>9</v>
-      </c>
-      <c r="Y404" t="s">
-        <v>768</v>
-      </c>
-      <c r="Z404">
-        <v>0</v>
-      </c>
-      <c r="AA404" t="s">
-        <v>1621</v>
-      </c>
-      <c r="AB404" t="s">
-        <v>1622</v>
-      </c>
-      <c r="AC404" t="s">
-        <v>1016</v>
-      </c>
-      <c r="AD404" t="s">
-        <v>1249</v>
-      </c>
-      <c r="AE404">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="405" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="405" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A405">
         <v>272</v>
       </c>
@@ -35247,61 +32367,16 @@
         <v>270</v>
       </c>
       <c r="C405" t="s">
+        <v>1638</v>
+      </c>
+      <c r="D405">
+        <v>10000</v>
+      </c>
+      <c r="L405" t="s">
         <v>1592</v>
       </c>
-      <c r="F405" t="s">
-        <v>1593</v>
-      </c>
-      <c r="L405" t="s">
-        <v>1593</v>
-      </c>
-      <c r="M405" t="s">
-        <v>1782</v>
-      </c>
-      <c r="N405" t="s">
-        <v>1783</v>
-      </c>
-      <c r="O405" t="s">
-        <v>1784</v>
-      </c>
-      <c r="P405" t="s">
-        <v>1759</v>
-      </c>
-      <c r="Q405" t="s">
-        <v>1668</v>
-      </c>
-      <c r="R405" t="s">
-        <v>1785</v>
-      </c>
-      <c r="S405" t="s">
-        <v>619</v>
-      </c>
-      <c r="T405" t="s">
-        <v>1632</v>
-      </c>
-      <c r="U405">
-        <v>1</v>
-      </c>
-      <c r="V405">
-        <v>1</v>
-      </c>
-      <c r="W405">
-        <v>1</v>
-      </c>
-      <c r="X405">
-        <v>1</v>
-      </c>
-      <c r="Y405" t="s">
-        <v>619</v>
-      </c>
-      <c r="Z405">
-        <v>0</v>
-      </c>
-      <c r="AA405" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="406" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="406" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A406">
         <v>273</v>
       </c>
@@ -35309,61 +32384,16 @@
         <v>271</v>
       </c>
       <c r="C406" t="s">
+        <v>1639</v>
+      </c>
+      <c r="D406">
+        <v>10000</v>
+      </c>
+      <c r="L406" t="s">
         <v>1592</v>
       </c>
-      <c r="F406" t="s">
-        <v>1593</v>
-      </c>
-      <c r="L406" t="s">
-        <v>1593</v>
-      </c>
-      <c r="M406" t="s">
-        <v>1786</v>
-      </c>
-      <c r="N406" t="s">
-        <v>1787</v>
-      </c>
-      <c r="O406" t="s">
-        <v>1784</v>
-      </c>
-      <c r="P406" t="s">
-        <v>1759</v>
-      </c>
-      <c r="Q406" t="s">
-        <v>1788</v>
-      </c>
-      <c r="R406" t="s">
-        <v>1785</v>
-      </c>
-      <c r="S406" t="s">
-        <v>619</v>
-      </c>
-      <c r="T406" t="s">
-        <v>1632</v>
-      </c>
-      <c r="U406">
-        <v>1</v>
-      </c>
-      <c r="V406">
-        <v>1</v>
-      </c>
-      <c r="W406">
-        <v>1</v>
-      </c>
-      <c r="X406">
-        <v>1</v>
-      </c>
-      <c r="Y406" t="s">
-        <v>619</v>
-      </c>
-      <c r="Z406">
-        <v>0</v>
-      </c>
-      <c r="AA406" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="407" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="407" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A407">
         <v>281</v>
       </c>
@@ -35371,61 +32401,16 @@
         <v>280</v>
       </c>
       <c r="C407" t="s">
+        <v>1640</v>
+      </c>
+      <c r="D407">
+        <v>10000</v>
+      </c>
+      <c r="L407" t="s">
         <v>1592</v>
       </c>
-      <c r="F407" t="s">
-        <v>1593</v>
-      </c>
-      <c r="L407" t="s">
-        <v>1593</v>
-      </c>
-      <c r="M407" t="s">
-        <v>1789</v>
-      </c>
-      <c r="N407" t="s">
-        <v>1727</v>
-      </c>
-      <c r="O407" t="s">
-        <v>1625</v>
-      </c>
-      <c r="P407" t="s">
-        <v>1662</v>
-      </c>
-      <c r="Q407" t="s">
-        <v>1468</v>
-      </c>
-      <c r="R407" t="s">
-        <v>1790</v>
-      </c>
-      <c r="S407" t="s">
-        <v>619</v>
-      </c>
-      <c r="T407" t="s">
-        <v>1632</v>
-      </c>
-      <c r="U407">
-        <v>1</v>
-      </c>
-      <c r="V407">
-        <v>1</v>
-      </c>
-      <c r="W407">
-        <v>1</v>
-      </c>
-      <c r="X407">
-        <v>1</v>
-      </c>
-      <c r="Y407" t="s">
-        <v>619</v>
-      </c>
-      <c r="Z407">
-        <v>0</v>
-      </c>
-      <c r="AA407" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="408" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="408" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A408">
         <v>282</v>
       </c>
@@ -35433,61 +32418,16 @@
         <v>279</v>
       </c>
       <c r="C408" t="s">
+        <v>1641</v>
+      </c>
+      <c r="D408">
+        <v>10000</v>
+      </c>
+      <c r="L408" t="s">
         <v>1592</v>
       </c>
-      <c r="F408" t="s">
-        <v>1593</v>
-      </c>
-      <c r="L408" t="s">
-        <v>1593</v>
-      </c>
-      <c r="M408" t="s">
-        <v>1791</v>
-      </c>
-      <c r="N408" t="s">
-        <v>1792</v>
-      </c>
-      <c r="O408" t="s">
-        <v>1625</v>
-      </c>
-      <c r="P408" t="s">
-        <v>1793</v>
-      </c>
-      <c r="Q408" t="s">
-        <v>1641</v>
-      </c>
-      <c r="R408" t="s">
-        <v>1794</v>
-      </c>
-      <c r="S408" t="s">
-        <v>619</v>
-      </c>
-      <c r="T408" t="s">
-        <v>1632</v>
-      </c>
-      <c r="U408">
-        <v>1</v>
-      </c>
-      <c r="V408">
-        <v>1</v>
-      </c>
-      <c r="W408">
-        <v>1</v>
-      </c>
-      <c r="X408">
-        <v>1</v>
-      </c>
-      <c r="Y408" t="s">
-        <v>619</v>
-      </c>
-      <c r="Z408">
-        <v>0</v>
-      </c>
-      <c r="AA408" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="409" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="409" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A409">
         <v>282</v>
       </c>
@@ -35495,73 +32435,16 @@
         <v>281</v>
       </c>
       <c r="C409" t="s">
+        <v>1642</v>
+      </c>
+      <c r="D409">
+        <v>10000</v>
+      </c>
+      <c r="L409" t="s">
         <v>1592</v>
       </c>
-      <c r="F409" t="s">
-        <v>1593</v>
-      </c>
-      <c r="L409" t="s">
-        <v>1593</v>
-      </c>
-      <c r="M409" t="s">
-        <v>1795</v>
-      </c>
-      <c r="N409" t="s">
-        <v>1667</v>
-      </c>
-      <c r="O409" t="s">
-        <v>1736</v>
-      </c>
-      <c r="P409" t="s">
-        <v>1615</v>
-      </c>
-      <c r="Q409" t="s">
-        <v>1796</v>
-      </c>
-      <c r="R409" t="s">
-        <v>1771</v>
-      </c>
-      <c r="S409" t="s">
-        <v>628</v>
-      </c>
-      <c r="T409" t="s">
-        <v>1797</v>
-      </c>
-      <c r="U409">
-        <v>1</v>
-      </c>
-      <c r="V409">
-        <v>21</v>
-      </c>
-      <c r="W409">
-        <v>11</v>
-      </c>
-      <c r="X409">
-        <v>9</v>
-      </c>
-      <c r="Y409" t="s">
-        <v>768</v>
-      </c>
-      <c r="Z409">
-        <v>0</v>
-      </c>
-      <c r="AA409" t="s">
-        <v>1621</v>
-      </c>
-      <c r="AB409" t="s">
-        <v>1622</v>
-      </c>
-      <c r="AC409" t="s">
-        <v>1016</v>
-      </c>
-      <c r="AD409" t="s">
-        <v>1249</v>
-      </c>
-      <c r="AE409">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="410" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="410" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A410">
         <v>294</v>
       </c>
@@ -35569,61 +32452,16 @@
         <v>292</v>
       </c>
       <c r="C410" t="s">
+        <v>1643</v>
+      </c>
+      <c r="D410">
+        <v>10000</v>
+      </c>
+      <c r="L410" t="s">
         <v>1592</v>
       </c>
-      <c r="F410" t="s">
-        <v>1593</v>
-      </c>
-      <c r="L410" t="s">
-        <v>1593</v>
-      </c>
-      <c r="M410" t="s">
-        <v>1798</v>
-      </c>
-      <c r="N410" t="s">
-        <v>1799</v>
-      </c>
-      <c r="O410" t="s">
-        <v>1625</v>
-      </c>
-      <c r="P410" t="s">
-        <v>1800</v>
-      </c>
-      <c r="Q410" t="s">
-        <v>1801</v>
-      </c>
-      <c r="R410" t="s">
-        <v>1802</v>
-      </c>
-      <c r="S410" t="s">
-        <v>619</v>
-      </c>
-      <c r="T410" t="s">
-        <v>1632</v>
-      </c>
-      <c r="U410">
-        <v>1</v>
-      </c>
-      <c r="V410">
-        <v>1</v>
-      </c>
-      <c r="W410">
-        <v>1</v>
-      </c>
-      <c r="X410">
-        <v>1</v>
-      </c>
-      <c r="Y410" t="s">
-        <v>619</v>
-      </c>
-      <c r="Z410">
-        <v>0</v>
-      </c>
-      <c r="AA410" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="411" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="411" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A411">
         <v>303</v>
       </c>
@@ -35631,61 +32469,16 @@
         <v>300</v>
       </c>
       <c r="C411" t="s">
+        <v>1644</v>
+      </c>
+      <c r="D411">
+        <v>10000</v>
+      </c>
+      <c r="L411" t="s">
         <v>1592</v>
       </c>
-      <c r="F411" t="s">
-        <v>1593</v>
-      </c>
-      <c r="L411" t="s">
-        <v>1593</v>
-      </c>
-      <c r="M411" t="s">
-        <v>1803</v>
-      </c>
-      <c r="N411" t="s">
-        <v>1804</v>
-      </c>
-      <c r="O411" t="s">
-        <v>1625</v>
-      </c>
-      <c r="P411" t="s">
-        <v>1793</v>
-      </c>
-      <c r="Q411" t="s">
-        <v>1805</v>
-      </c>
-      <c r="R411" t="s">
-        <v>1794</v>
-      </c>
-      <c r="S411" t="s">
-        <v>619</v>
-      </c>
-      <c r="T411" t="s">
-        <v>1632</v>
-      </c>
-      <c r="U411">
-        <v>1</v>
-      </c>
-      <c r="V411">
-        <v>1</v>
-      </c>
-      <c r="W411">
-        <v>1</v>
-      </c>
-      <c r="X411">
-        <v>1</v>
-      </c>
-      <c r="Y411" t="s">
-        <v>619</v>
-      </c>
-      <c r="Z411">
-        <v>0</v>
-      </c>
-      <c r="AA411" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="412" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="412" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A412">
         <v>308</v>
       </c>
@@ -35693,61 +32486,16 @@
         <v>309</v>
       </c>
       <c r="C412" t="s">
+        <v>1645</v>
+      </c>
+      <c r="D412">
+        <v>10000</v>
+      </c>
+      <c r="L412" t="s">
         <v>1592</v>
       </c>
-      <c r="F412" t="s">
-        <v>1593</v>
-      </c>
-      <c r="L412" t="s">
-        <v>1593</v>
-      </c>
-      <c r="M412" t="s">
-        <v>1806</v>
-      </c>
-      <c r="N412" t="s">
-        <v>1807</v>
-      </c>
-      <c r="O412" t="s">
-        <v>1807</v>
-      </c>
-      <c r="P412" t="s">
-        <v>1697</v>
-      </c>
-      <c r="Q412" t="s">
-        <v>1309</v>
-      </c>
-      <c r="R412" t="s">
-        <v>1632</v>
-      </c>
-      <c r="S412" t="s">
-        <v>619</v>
-      </c>
-      <c r="T412" t="s">
-        <v>1632</v>
-      </c>
-      <c r="U412">
-        <v>0</v>
-      </c>
-      <c r="V412">
-        <v>0</v>
-      </c>
-      <c r="W412">
-        <v>0</v>
-      </c>
-      <c r="X412">
-        <v>0</v>
-      </c>
-      <c r="Y412" t="s">
-        <v>619</v>
-      </c>
-      <c r="Z412">
-        <v>0</v>
-      </c>
-      <c r="AA412" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="413" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="413" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A413">
         <v>312</v>
       </c>
@@ -35755,61 +32503,16 @@
         <v>310</v>
       </c>
       <c r="C413" t="s">
+        <v>1646</v>
+      </c>
+      <c r="D413">
+        <v>10000</v>
+      </c>
+      <c r="L413" t="s">
         <v>1592</v>
       </c>
-      <c r="F413" t="s">
-        <v>1593</v>
-      </c>
-      <c r="L413" t="s">
-        <v>1593</v>
-      </c>
-      <c r="M413" t="s">
-        <v>1808</v>
-      </c>
-      <c r="N413" t="s">
-        <v>1809</v>
-      </c>
-      <c r="O413" t="s">
-        <v>1810</v>
-      </c>
-      <c r="P413" t="s">
-        <v>1811</v>
-      </c>
-      <c r="Q413" t="s">
-        <v>1812</v>
-      </c>
-      <c r="R413" t="s">
-        <v>1813</v>
-      </c>
-      <c r="S413" t="s">
-        <v>619</v>
-      </c>
-      <c r="T413" t="s">
-        <v>1632</v>
-      </c>
-      <c r="U413">
-        <v>1</v>
-      </c>
-      <c r="V413">
-        <v>1</v>
-      </c>
-      <c r="W413">
-        <v>1</v>
-      </c>
-      <c r="X413">
-        <v>1</v>
-      </c>
-      <c r="Y413" t="s">
-        <v>619</v>
-      </c>
-      <c r="Z413">
-        <v>0</v>
-      </c>
-      <c r="AA413" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="414" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="414" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A414">
         <v>316</v>
       </c>
@@ -35817,73 +32520,16 @@
         <v>311</v>
       </c>
       <c r="C414" t="s">
+        <v>1647</v>
+      </c>
+      <c r="D414">
+        <v>10000</v>
+      </c>
+      <c r="L414" t="s">
         <v>1592</v>
       </c>
-      <c r="F414" t="s">
-        <v>1593</v>
-      </c>
-      <c r="L414" t="s">
-        <v>1593</v>
-      </c>
-      <c r="M414" t="s">
-        <v>1814</v>
-      </c>
-      <c r="N414" t="s">
-        <v>1667</v>
-      </c>
-      <c r="O414" t="s">
-        <v>1736</v>
-      </c>
-      <c r="P414" t="s">
-        <v>1615</v>
-      </c>
-      <c r="Q414" t="s">
-        <v>1773</v>
-      </c>
-      <c r="R414" t="s">
-        <v>1746</v>
-      </c>
-      <c r="S414" t="s">
-        <v>628</v>
-      </c>
-      <c r="T414" t="s">
-        <v>1774</v>
-      </c>
-      <c r="U414">
-        <v>1</v>
-      </c>
-      <c r="V414">
-        <v>21</v>
-      </c>
-      <c r="W414">
-        <v>11</v>
-      </c>
-      <c r="X414">
-        <v>9</v>
-      </c>
-      <c r="Y414" t="s">
-        <v>768</v>
-      </c>
-      <c r="Z414">
-        <v>0</v>
-      </c>
-      <c r="AA414" t="s">
-        <v>1621</v>
-      </c>
-      <c r="AB414" t="s">
-        <v>1622</v>
-      </c>
-      <c r="AC414" t="s">
-        <v>1016</v>
-      </c>
-      <c r="AD414" t="s">
-        <v>1249</v>
-      </c>
-      <c r="AE414">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="415" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="415" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A415">
         <v>323</v>
       </c>
@@ -35891,73 +32537,16 @@
         <v>321</v>
       </c>
       <c r="C415" t="s">
+        <v>1648</v>
+      </c>
+      <c r="D415">
+        <v>10000</v>
+      </c>
+      <c r="L415" t="s">
         <v>1592</v>
       </c>
-      <c r="F415" t="s">
-        <v>1593</v>
-      </c>
-      <c r="L415" t="s">
-        <v>1593</v>
-      </c>
-      <c r="M415" t="s">
-        <v>1815</v>
-      </c>
-      <c r="N415" t="s">
-        <v>1667</v>
-      </c>
-      <c r="O415" t="s">
-        <v>1736</v>
-      </c>
-      <c r="P415" t="s">
-        <v>1615</v>
-      </c>
-      <c r="Q415" t="s">
-        <v>1816</v>
-      </c>
-      <c r="R415" t="s">
-        <v>1746</v>
-      </c>
-      <c r="S415" t="s">
-        <v>628</v>
-      </c>
-      <c r="T415" t="s">
-        <v>1817</v>
-      </c>
-      <c r="U415">
-        <v>1</v>
-      </c>
-      <c r="V415">
-        <v>21</v>
-      </c>
-      <c r="W415">
-        <v>11</v>
-      </c>
-      <c r="X415">
-        <v>9</v>
-      </c>
-      <c r="Y415" t="s">
-        <v>768</v>
-      </c>
-      <c r="Z415">
-        <v>0</v>
-      </c>
-      <c r="AA415" t="s">
-        <v>1621</v>
-      </c>
-      <c r="AB415" t="s">
-        <v>1622</v>
-      </c>
-      <c r="AC415" t="s">
-        <v>1016</v>
-      </c>
-      <c r="AD415" t="s">
-        <v>1249</v>
-      </c>
-      <c r="AE415">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="416" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="416" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A416">
         <v>323</v>
       </c>
@@ -35965,73 +32554,16 @@
         <v>322</v>
       </c>
       <c r="C416" t="s">
+        <v>1649</v>
+      </c>
+      <c r="D416">
+        <v>10000</v>
+      </c>
+      <c r="L416" t="s">
         <v>1592</v>
       </c>
-      <c r="F416" t="s">
-        <v>1593</v>
-      </c>
-      <c r="L416" t="s">
-        <v>1593</v>
-      </c>
-      <c r="M416" t="s">
-        <v>1818</v>
-      </c>
-      <c r="N416" t="s">
-        <v>1667</v>
-      </c>
-      <c r="O416" t="s">
-        <v>1741</v>
-      </c>
-      <c r="P416" t="s">
-        <v>1605</v>
-      </c>
-      <c r="Q416" t="s">
-        <v>1819</v>
-      </c>
-      <c r="R416" t="s">
-        <v>1742</v>
-      </c>
-      <c r="S416" t="s">
-        <v>628</v>
-      </c>
-      <c r="T416" t="s">
-        <v>1743</v>
-      </c>
-      <c r="U416">
-        <v>1</v>
-      </c>
-      <c r="V416">
-        <v>21</v>
-      </c>
-      <c r="W416">
-        <v>11</v>
-      </c>
-      <c r="X416">
-        <v>9</v>
-      </c>
-      <c r="Y416" t="s">
-        <v>620</v>
-      </c>
-      <c r="Z416">
-        <v>0</v>
-      </c>
-      <c r="AA416" t="s">
-        <v>1621</v>
-      </c>
-      <c r="AB416" t="s">
-        <v>1622</v>
-      </c>
-      <c r="AC416" t="s">
-        <v>1092</v>
-      </c>
-      <c r="AD416" t="s">
-        <v>1478</v>
-      </c>
-      <c r="AE416">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="417" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="417" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A417">
         <v>323</v>
       </c>
@@ -36039,73 +32571,16 @@
         <v>322</v>
       </c>
       <c r="C417" t="s">
+        <v>1650</v>
+      </c>
+      <c r="D417">
+        <v>10000</v>
+      </c>
+      <c r="L417" t="s">
         <v>1592</v>
       </c>
-      <c r="F417" t="s">
-        <v>1593</v>
-      </c>
-      <c r="L417" t="s">
-        <v>1593</v>
-      </c>
-      <c r="M417" t="s">
-        <v>1820</v>
-      </c>
-      <c r="N417" t="s">
-        <v>1667</v>
-      </c>
-      <c r="O417" t="s">
-        <v>1741</v>
-      </c>
-      <c r="P417" t="s">
-        <v>1605</v>
-      </c>
-      <c r="Q417" t="s">
-        <v>1668</v>
-      </c>
-      <c r="R417" t="s">
-        <v>1821</v>
-      </c>
-      <c r="S417" t="s">
-        <v>628</v>
-      </c>
-      <c r="T417" t="s">
-        <v>1822</v>
-      </c>
-      <c r="U417">
-        <v>1</v>
-      </c>
-      <c r="V417">
-        <v>21</v>
-      </c>
-      <c r="W417">
-        <v>11</v>
-      </c>
-      <c r="X417">
-        <v>9</v>
-      </c>
-      <c r="Y417" t="s">
-        <v>620</v>
-      </c>
-      <c r="Z417">
-        <v>0</v>
-      </c>
-      <c r="AA417" t="s">
-        <v>1621</v>
-      </c>
-      <c r="AB417" t="s">
-        <v>1622</v>
-      </c>
-      <c r="AC417" t="s">
-        <v>1092</v>
-      </c>
-      <c r="AD417" t="s">
-        <v>1478</v>
-      </c>
-      <c r="AE417">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="418" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="418" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A418">
         <v>327</v>
       </c>
@@ -36113,73 +32588,16 @@
         <v>326</v>
       </c>
       <c r="C418" t="s">
+        <v>1651</v>
+      </c>
+      <c r="D418">
+        <v>10000</v>
+      </c>
+      <c r="L418" t="s">
         <v>1592</v>
       </c>
-      <c r="F418" t="s">
-        <v>1593</v>
-      </c>
-      <c r="L418" t="s">
-        <v>1593</v>
-      </c>
-      <c r="M418" t="s">
-        <v>1823</v>
-      </c>
-      <c r="N418" t="s">
-        <v>1667</v>
-      </c>
-      <c r="O418" t="s">
-        <v>1736</v>
-      </c>
-      <c r="P418" t="s">
-        <v>1615</v>
-      </c>
-      <c r="Q418" t="s">
-        <v>1722</v>
-      </c>
-      <c r="R418" t="s">
-        <v>1824</v>
-      </c>
-      <c r="S418" t="s">
-        <v>628</v>
-      </c>
-      <c r="T418" t="s">
-        <v>1825</v>
-      </c>
-      <c r="U418">
-        <v>1</v>
-      </c>
-      <c r="V418">
-        <v>21</v>
-      </c>
-      <c r="W418">
-        <v>11</v>
-      </c>
-      <c r="X418">
-        <v>9</v>
-      </c>
-      <c r="Y418" t="s">
-        <v>768</v>
-      </c>
-      <c r="Z418">
-        <v>0</v>
-      </c>
-      <c r="AA418" t="s">
-        <v>1621</v>
-      </c>
-      <c r="AB418" t="s">
-        <v>1622</v>
-      </c>
-      <c r="AC418" t="s">
-        <v>1016</v>
-      </c>
-      <c r="AD418" t="s">
-        <v>1249</v>
-      </c>
-      <c r="AE418">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="419" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="419" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A419">
         <v>338</v>
       </c>
@@ -36187,279 +32605,195 @@
         <v>337</v>
       </c>
       <c r="C419" t="s">
+        <v>1652</v>
+      </c>
+      <c r="D419">
+        <v>10000</v>
+      </c>
+      <c r="L419" t="s">
         <v>1592</v>
       </c>
-      <c r="F419" t="s">
-        <v>1593</v>
-      </c>
-      <c r="L419" t="s">
-        <v>1593</v>
-      </c>
-      <c r="M419" t="s">
-        <v>1826</v>
-      </c>
-      <c r="N419" t="s">
-        <v>1827</v>
-      </c>
-      <c r="O419" t="s">
-        <v>1784</v>
-      </c>
-      <c r="P419" t="s">
-        <v>1828</v>
-      </c>
-      <c r="Q419" t="s">
-        <v>1829</v>
-      </c>
-      <c r="R419" t="s">
-        <v>1830</v>
-      </c>
-      <c r="S419" t="s">
-        <v>619</v>
-      </c>
-      <c r="T419" t="s">
-        <v>1632</v>
-      </c>
-      <c r="U419">
-        <v>1</v>
-      </c>
-      <c r="V419">
-        <v>1</v>
-      </c>
-      <c r="W419">
-        <v>1</v>
-      </c>
-      <c r="X419">
-        <v>1</v>
-      </c>
-      <c r="Y419" t="s">
-        <v>619</v>
-      </c>
-      <c r="Z419">
-        <v>0</v>
-      </c>
-      <c r="AA419" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="420" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="420" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A420">
         <v>70</v>
       </c>
       <c r="B420">
         <v>64</v>
       </c>
-      <c r="C420" t="s">
-        <v>1831</v>
-      </c>
-      <c r="F420" t="s">
-        <v>1593</v>
+      <c r="D420">
+        <v>10000</v>
       </c>
       <c r="L420" t="s">
-        <v>1593</v>
-      </c>
-    </row>
-    <row r="421" spans="1:31" x14ac:dyDescent="0.3">
+        <v>1592</v>
+      </c>
+    </row>
+    <row r="421" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A421">
         <v>64</v>
       </c>
       <c r="B421">
         <v>65</v>
       </c>
-      <c r="C421" t="s">
-        <v>1831</v>
-      </c>
-      <c r="F421" t="s">
-        <v>1593</v>
+      <c r="D421">
+        <v>10000</v>
       </c>
       <c r="L421" t="s">
-        <v>1593</v>
-      </c>
-    </row>
-    <row r="422" spans="1:31" x14ac:dyDescent="0.3">
+        <v>1592</v>
+      </c>
+    </row>
+    <row r="422" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A422">
         <v>96</v>
       </c>
       <c r="B422">
         <v>95</v>
       </c>
-      <c r="C422" t="s">
-        <v>1831</v>
-      </c>
-      <c r="F422" t="s">
-        <v>1593</v>
+      <c r="D422">
+        <v>10000</v>
       </c>
       <c r="L422" t="s">
-        <v>1593</v>
-      </c>
-    </row>
-    <row r="423" spans="1:31" x14ac:dyDescent="0.3">
+        <v>1592</v>
+      </c>
+    </row>
+    <row r="423" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A423">
         <v>95</v>
       </c>
       <c r="B423">
         <v>93</v>
       </c>
-      <c r="C423" t="s">
-        <v>1831</v>
-      </c>
-      <c r="F423" t="s">
-        <v>1593</v>
+      <c r="D423">
+        <v>10000</v>
       </c>
       <c r="L423" t="s">
-        <v>1593</v>
-      </c>
-    </row>
-    <row r="424" spans="1:31" x14ac:dyDescent="0.3">
+        <v>1592</v>
+      </c>
+    </row>
+    <row r="424" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A424">
         <v>96</v>
       </c>
       <c r="B424">
         <v>95</v>
       </c>
-      <c r="C424" t="s">
-        <v>1831</v>
-      </c>
-      <c r="F424" t="s">
-        <v>1593</v>
+      <c r="D424">
+        <v>10000</v>
       </c>
       <c r="L424" t="s">
-        <v>1593</v>
-      </c>
-    </row>
-    <row r="425" spans="1:31" x14ac:dyDescent="0.3">
+        <v>1592</v>
+      </c>
+    </row>
+    <row r="425" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A425">
         <v>95</v>
       </c>
       <c r="B425">
         <v>94</v>
       </c>
-      <c r="C425" t="s">
-        <v>1831</v>
-      </c>
-      <c r="F425" t="s">
-        <v>1593</v>
+      <c r="D425">
+        <v>10000</v>
       </c>
       <c r="L425" t="s">
-        <v>1593</v>
-      </c>
-    </row>
-    <row r="426" spans="1:31" x14ac:dyDescent="0.3">
+        <v>1592</v>
+      </c>
+    </row>
+    <row r="426" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A426">
         <v>108</v>
       </c>
       <c r="B426">
         <v>107</v>
       </c>
-      <c r="C426" t="s">
-        <v>1831</v>
-      </c>
-      <c r="F426" t="s">
-        <v>1593</v>
+      <c r="D426">
+        <v>10000</v>
       </c>
       <c r="L426" t="s">
-        <v>1593</v>
-      </c>
-    </row>
-    <row r="427" spans="1:31" x14ac:dyDescent="0.3">
+        <v>1592</v>
+      </c>
+    </row>
+    <row r="427" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A427">
         <v>107</v>
       </c>
       <c r="B427">
         <v>106</v>
       </c>
-      <c r="C427" t="s">
-        <v>1831</v>
-      </c>
-      <c r="F427" t="s">
-        <v>1593</v>
+      <c r="D427">
+        <v>10000</v>
       </c>
       <c r="L427" t="s">
-        <v>1593</v>
-      </c>
-    </row>
-    <row r="428" spans="1:31" x14ac:dyDescent="0.3">
+        <v>1592</v>
+      </c>
+    </row>
+    <row r="428" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A428">
         <v>134</v>
       </c>
       <c r="B428">
         <v>133</v>
       </c>
-      <c r="C428" t="s">
-        <v>1831</v>
-      </c>
-      <c r="F428" t="s">
-        <v>1593</v>
+      <c r="D428">
+        <v>10000</v>
       </c>
       <c r="L428" t="s">
-        <v>1593</v>
-      </c>
-    </row>
-    <row r="429" spans="1:31" x14ac:dyDescent="0.3">
+        <v>1592</v>
+      </c>
+    </row>
+    <row r="429" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A429">
         <v>133</v>
       </c>
       <c r="B429">
         <v>132</v>
       </c>
-      <c r="C429" t="s">
-        <v>1831</v>
-      </c>
-      <c r="F429" t="s">
-        <v>1593</v>
+      <c r="D429">
+        <v>10000</v>
       </c>
       <c r="L429" t="s">
-        <v>1593</v>
-      </c>
-    </row>
-    <row r="430" spans="1:31" x14ac:dyDescent="0.3">
+        <v>1592</v>
+      </c>
+    </row>
+    <row r="430" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A430">
         <v>145</v>
       </c>
       <c r="B430">
         <v>137</v>
       </c>
-      <c r="C430" t="s">
-        <v>1831</v>
-      </c>
-      <c r="F430" t="s">
-        <v>1593</v>
+      <c r="D430">
+        <v>10000</v>
       </c>
       <c r="L430" t="s">
-        <v>1593</v>
-      </c>
-    </row>
-    <row r="431" spans="1:31" x14ac:dyDescent="0.3">
+        <v>1592</v>
+      </c>
+    </row>
+    <row r="431" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A431">
         <v>137</v>
       </c>
       <c r="B431">
         <v>139</v>
       </c>
-      <c r="C431" t="s">
-        <v>1831</v>
-      </c>
-      <c r="F431" t="s">
-        <v>1593</v>
+      <c r="D431">
+        <v>10000</v>
       </c>
       <c r="L431" t="s">
-        <v>1593</v>
-      </c>
-    </row>
-    <row r="432" spans="1:31" x14ac:dyDescent="0.3">
+        <v>1592</v>
+      </c>
+    </row>
+    <row r="432" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A432">
         <v>214</v>
       </c>
       <c r="B432">
         <v>209</v>
       </c>
-      <c r="C432" t="s">
-        <v>1831</v>
-      </c>
-      <c r="F432" t="s">
-        <v>1593</v>
+      <c r="D432">
+        <v>10000</v>
       </c>
       <c r="L432" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="433" spans="1:12" x14ac:dyDescent="0.3">
@@ -36469,14 +32803,11 @@
       <c r="B433">
         <v>208</v>
       </c>
-      <c r="C433" t="s">
-        <v>1831</v>
-      </c>
-      <c r="F433" t="s">
-        <v>1593</v>
+      <c r="D433">
+        <v>10000</v>
       </c>
       <c r="L433" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="434" spans="1:12" x14ac:dyDescent="0.3">
@@ -36486,14 +32817,11 @@
       <c r="B434">
         <v>219</v>
       </c>
-      <c r="C434" t="s">
-        <v>1831</v>
-      </c>
-      <c r="F434" t="s">
-        <v>1593</v>
+      <c r="D434">
+        <v>10000</v>
       </c>
       <c r="L434" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="435" spans="1:12" x14ac:dyDescent="0.3">
@@ -36503,14 +32831,11 @@
       <c r="B435">
         <v>218</v>
       </c>
-      <c r="C435" t="s">
-        <v>1831</v>
-      </c>
-      <c r="F435" t="s">
-        <v>1593</v>
+      <c r="D435">
+        <v>10000</v>
       </c>
       <c r="L435" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="436" spans="1:12" x14ac:dyDescent="0.3">
@@ -36520,14 +32845,11 @@
       <c r="B436">
         <v>312</v>
       </c>
-      <c r="C436" t="s">
-        <v>1831</v>
-      </c>
-      <c r="F436" t="s">
-        <v>1593</v>
+      <c r="D436">
+        <v>10000</v>
       </c>
       <c r="L436" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="437" spans="1:12" x14ac:dyDescent="0.3">
@@ -36537,14 +32859,11 @@
       <c r="B437">
         <v>309</v>
       </c>
-      <c r="C437" t="s">
-        <v>1831</v>
-      </c>
-      <c r="F437" t="s">
-        <v>1593</v>
+      <c r="D437">
+        <v>10000</v>
       </c>
       <c r="L437" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="438" spans="1:12" x14ac:dyDescent="0.3">
@@ -36554,14 +32873,11 @@
       <c r="B438">
         <v>325</v>
       </c>
-      <c r="C438" t="s">
-        <v>1831</v>
-      </c>
-      <c r="F438" t="s">
-        <v>1593</v>
+      <c r="D438">
+        <v>10000</v>
       </c>
       <c r="L438" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="439" spans="1:12" x14ac:dyDescent="0.3">
@@ -36571,17 +32887,15 @@
       <c r="B439">
         <v>324</v>
       </c>
-      <c r="C439" t="s">
-        <v>1831</v>
-      </c>
-      <c r="F439" t="s">
-        <v>1593</v>
+      <c r="D439">
+        <v>10000</v>
       </c>
       <c r="L439" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AE439" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>